--- a/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2585.07</v>
+        <v>37864.53</v>
       </c>
       <c r="C4" t="n">
-        <v>559944</v>
+        <v>6139224</v>
       </c>
       <c r="D4" t="n">
-        <v>439956</v>
+        <v>4823676</v>
       </c>
       <c r="E4" t="n">
-        <v>123300</v>
+        <v>1446300</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>6480</v>
+        <v>101340</v>
       </c>
       <c r="H4" t="n">
-        <v>210</v>
+        <v>10890</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>19200</v>
+        <v>264180</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3677.49</v>
+        <v>41175.18</v>
       </c>
       <c r="C5" t="n">
-        <v>589680</v>
+        <v>4066272</v>
       </c>
       <c r="D5" t="n">
-        <v>463320</v>
+        <v>3194928</v>
       </c>
       <c r="E5" t="n">
-        <v>95400</v>
+        <v>586800</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>9450</v>
+        <v>97560</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>11970</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>22650</v>
+        <v>208500</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3665.43</v>
+        <v>23141.97</v>
       </c>
       <c r="C6" t="n">
-        <v>354816</v>
+        <v>1422288</v>
       </c>
       <c r="D6" t="n">
-        <v>278784</v>
+        <v>1117512</v>
       </c>
       <c r="E6" t="n">
-        <v>58500</v>
+        <v>92700</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>6210</v>
+        <v>41160</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>18240</v>
+        <v>81180</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2393.64</v>
+        <v>7601.13</v>
       </c>
       <c r="C7" t="n">
-        <v>169344</v>
+        <v>555408</v>
       </c>
       <c r="D7" t="n">
-        <v>133056</v>
+        <v>436392</v>
       </c>
       <c r="E7" t="n">
-        <v>23400</v>
+        <v>26100</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4740</v>
+        <v>10950</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7200</v>
+        <v>36450</v>
       </c>
     </row>
     <row r="8">
@@ -9995,22 +9989,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1268.82</v>
+        <v>1436.49</v>
       </c>
       <c r="C8" t="n">
-        <v>52416</v>
+        <v>110376</v>
       </c>
       <c r="D8" t="n">
-        <v>41184</v>
+        <v>86724</v>
       </c>
       <c r="E8" t="n">
-        <v>5400</v>
+        <v>2700</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1410</v>
+        <v>1470</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -10025,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3600</v>
+        <v>10890</v>
       </c>
     </row>
     <row r="9">
@@ -10033,22 +10027,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>621.1799999999999</v>
+        <v>232.38</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>17136</v>
       </c>
       <c r="D9" t="n">
-        <v>13860</v>
+        <v>13464</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>900</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>840</v>
+        <v>540</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10063,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>780</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="10">
@@ -10071,25 +10065,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>383.04</v>
+        <v>185.22</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>3024</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>2376</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>480</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="11">
@@ -10109,13 +10103,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.01</v>
+        <v>62.55</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>2520</v>
       </c>
       <c r="D11" t="n">
-        <v>2376</v>
+        <v>1980</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10124,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="12">
@@ -10147,13 +10141,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>157.05</v>
+        <v>22.95</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="D12" t="n">
-        <v>792</v>
+        <v>396</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10162,7 +10156,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.57</v>
+        <v>13.59</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14">
@@ -10223,13 +10217,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>6.12</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1188</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -10238,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>2.88</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3720</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0.27</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10337,7 +10331,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10454,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1654.87</v>
+        <v>18528.83</v>
       </c>
       <c r="C5" t="n">
-        <v>324324</v>
+        <v>2236449.6</v>
       </c>
       <c r="D5" t="n">
-        <v>153358.92</v>
+        <v>1057521.17</v>
       </c>
       <c r="E5" t="n">
-        <v>10522.62</v>
+        <v>64724.04</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4309.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4756.5</v>
+        <v>43785</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2932.34</v>
+        <v>18513.58</v>
       </c>
       <c r="C6" t="n">
-        <v>319334.4</v>
+        <v>1280059.2</v>
       </c>
       <c r="D6" t="n">
-        <v>141343.49</v>
+        <v>566578.58</v>
       </c>
       <c r="E6" t="n">
-        <v>9886.5</v>
+        <v>15666.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G6" t="n">
-        <v>310.5</v>
+        <v>2058</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>786.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6748.8</v>
+        <v>30036.6</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2273.96</v>
+        <v>7221.07</v>
       </c>
       <c r="C7" t="n">
-        <v>169344</v>
+        <v>555408</v>
       </c>
       <c r="D7" t="n">
-        <v>84889.73</v>
+        <v>278418.1</v>
       </c>
       <c r="E7" t="n">
-        <v>4977.18</v>
+        <v>5551.47</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>711</v>
+        <v>1642.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>306.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4320</v>
+        <v>21870</v>
       </c>
     </row>
     <row r="8">
@@ -11859,22 +11853,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1268.82</v>
+        <v>1436.49</v>
       </c>
       <c r="C8" t="n">
-        <v>52416</v>
+        <v>110376</v>
       </c>
       <c r="D8" t="n">
-        <v>30311.42</v>
+        <v>63828.86</v>
       </c>
       <c r="E8" t="n">
-        <v>1324.62</v>
+        <v>662.3099999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>916.5</v>
+        <v>955.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -11889,7 +11883,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2556</v>
+        <v>7731.9</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>621.1799999999999</v>
+        <v>232.38</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>17136</v>
       </c>
       <c r="D9" t="n">
-        <v>11129.58</v>
+        <v>10811.59</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>240.93</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>459</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11927,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>631.8</v>
+        <v>3280.5</v>
       </c>
     </row>
     <row r="10">
@@ -11935,25 +11929,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>383.04</v>
+        <v>185.22</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>3024</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>2067.12</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>427.2</v>
+        <v>2723.4</v>
       </c>
     </row>
     <row r="11">
@@ -11973,13 +11967,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.01</v>
+        <v>62.55</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>2520</v>
       </c>
       <c r="D11" t="n">
-        <v>2134.84</v>
+        <v>1779.03</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11988,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="12">
@@ -12011,13 +12005,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>157.05</v>
+        <v>22.95</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="D12" t="n">
-        <v>734.1799999999999</v>
+        <v>367.09</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12026,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.57</v>
+        <v>13.59</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1504.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14">
@@ -12087,13 +12081,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>6.12</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1154.74</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12102,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>2.88</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2733.19</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3720</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0.27</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12201,7 +12195,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12318,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3640715.1</v>
+        <v>40763428.2</v>
       </c>
       <c r="C5" t="n">
-        <v>17837820</v>
+        <v>123004728</v>
       </c>
       <c r="D5" t="n">
-        <v>15539859.36</v>
+        <v>107158619.95</v>
       </c>
       <c r="E5" t="n">
-        <v>1938687.51</v>
+        <v>11924757.13</v>
       </c>
       <c r="F5" t="n">
-        <v>5000.04</v>
+        <v>5833.38</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1192140.18</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>44806.23</v>
+        <v>412454.7</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>6451156.8</v>
+        <v>40729867.2</v>
       </c>
       <c r="C6" t="n">
-        <v>17563392</v>
+        <v>70403256</v>
       </c>
       <c r="D6" t="n">
-        <v>14322335.64</v>
+        <v>57411407.92</v>
       </c>
       <c r="E6" t="n">
-        <v>1821488.76</v>
+        <v>2886359.11</v>
       </c>
       <c r="F6" t="n">
-        <v>12500.1</v>
+        <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5744.25</v>
+        <v>38073</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>217612.89</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>29166.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>63573.7</v>
+        <v>282944.77</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>5002707.6</v>
+        <v>15886361.7</v>
       </c>
       <c r="C7" t="n">
-        <v>9313920</v>
+        <v>30547440</v>
       </c>
       <c r="D7" t="n">
-        <v>8601876.140000001</v>
+        <v>28212105.67</v>
       </c>
       <c r="E7" t="n">
-        <v>916995.64</v>
+        <v>1022802.83</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>13153.5</v>
+        <v>30386.25</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>84820.89</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>81666.2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>40694.4</v>
+        <v>206015.4</v>
       </c>
     </row>
     <row r="8">
@@ -12791,22 +12785,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2791404</v>
+        <v>3160278</v>
       </c>
       <c r="C8" t="n">
-        <v>2882880</v>
+        <v>6070680</v>
       </c>
       <c r="D8" t="n">
-        <v>3071456.59</v>
+        <v>6467778.79</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>122023.99</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>16955.25</v>
+        <v>17676.75</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12821,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>24077.52</v>
+        <v>72834.5</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1366596</v>
+        <v>511236</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>942480</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>1095538.62</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>44388.94</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13209</v>
+        <v>8491.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12859,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5951.56</v>
+        <v>30902.31</v>
       </c>
     </row>
     <row r="10">
@@ -12867,25 +12861,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>842688</v>
+        <v>407484</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>166320</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>209461.27</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>48086.64</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7215</v>
+        <v>6660</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4024.22</v>
+        <v>25654.43</v>
       </c>
     </row>
     <row r="11">
@@ -12905,13 +12899,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>473022</v>
+        <v>137610</v>
       </c>
       <c r="C11" t="n">
-        <v>166320</v>
+        <v>138600</v>
       </c>
       <c r="D11" t="n">
-        <v>216322.93</v>
+        <v>180269.11</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12920,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>4995</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>28542.6</v>
       </c>
     </row>
     <row r="12">
@@ -12943,13 +12937,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>345510</v>
+        <v>50490</v>
       </c>
       <c r="C12" t="n">
-        <v>55440</v>
+        <v>27720</v>
       </c>
       <c r="D12" t="n">
-        <v>74394.86</v>
+        <v>37197.43</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12958,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>3885</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>12151.8</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>370854</v>
+        <v>29898</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>152401.13</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2775</v>
+        <v>1665</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>1978.2</v>
       </c>
     </row>
     <row r="14">
@@ -13019,13 +13013,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>94248</v>
+        <v>13464</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>83160</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>117009.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13034,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7770</v>
+        <v>3885</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>7347.6</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>9504</v>
+        <v>6336</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>276954.35</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>68820</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>594</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1110</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13133,7 +13127,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>120380.04</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13250,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>200633.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>37864.53</v>
+        <v>16856.46</v>
       </c>
       <c r="C4" t="n">
-        <v>6139224</v>
+        <v>1824480</v>
       </c>
       <c r="D4" t="n">
-        <v>4823676</v>
+        <v>1433520</v>
       </c>
       <c r="E4" t="n">
-        <v>1446300</v>
+        <v>732600</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>101340</v>
+        <v>50160</v>
       </c>
       <c r="H4" t="n">
-        <v>10890</v>
+        <v>3990</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>264180</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>41175.18</v>
+        <v>3595.41</v>
       </c>
       <c r="C5" t="n">
-        <v>4066272</v>
+        <v>333144</v>
       </c>
       <c r="D5" t="n">
-        <v>3194928</v>
+        <v>261756</v>
       </c>
       <c r="E5" t="n">
-        <v>586800</v>
+        <v>166500</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>97560</v>
+        <v>10050</v>
       </c>
       <c r="H5" t="n">
-        <v>11970</v>
+        <v>1050</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>208500</v>
+        <v>47280</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>23141.97</v>
+        <v>303.93</v>
       </c>
       <c r="C6" t="n">
-        <v>1422288</v>
+        <v>46872</v>
       </c>
       <c r="D6" t="n">
-        <v>1117512</v>
+        <v>36828</v>
       </c>
       <c r="E6" t="n">
-        <v>92700</v>
+        <v>15300</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>41160</v>
+        <v>750</v>
       </c>
       <c r="H6" t="n">
-        <v>1380</v>
+        <v>210</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>81180</v>
+        <v>8370</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>7601.13</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>555408</v>
+        <v>7056</v>
       </c>
       <c r="D7" t="n">
-        <v>436392</v>
+        <v>5544</v>
       </c>
       <c r="E7" t="n">
-        <v>26100</v>
+        <v>1800</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>10950</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>36450</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8">
@@ -13723,22 +13717,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1436.49</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>110376</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>86724</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1470</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -13753,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>10890</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -13761,22 +13755,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>232.38</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>17136</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>13464</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>540</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13791,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4050</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -13799,25 +13793,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>185.22</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3060</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,13 +13831,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>62.55</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13852,7 +13846,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3030</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -13875,13 +13869,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>22.95</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13890,7 +13884,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>13.59</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,13 +13945,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13966,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14106,10 +14100,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14144,10 +14138,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14182,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>18528.83</v>
+        <v>1617.93</v>
       </c>
       <c r="C5" t="n">
-        <v>2236449.6</v>
+        <v>183229.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1057521.17</v>
+        <v>86641.24000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>64724.04</v>
+        <v>18364.95</v>
       </c>
       <c r="F5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4309.2</v>
+        <v>378</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>43785</v>
+        <v>9928.799999999999</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>18513.58</v>
+        <v>243.14</v>
       </c>
       <c r="C6" t="n">
-        <v>1280059.2</v>
+        <v>42184.8</v>
       </c>
       <c r="D6" t="n">
-        <v>566578.58</v>
+        <v>18671.8</v>
       </c>
       <c r="E6" t="n">
-        <v>15666.3</v>
+        <v>2585.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2058</v>
+        <v>37.5</v>
       </c>
       <c r="H6" t="n">
-        <v>786.6</v>
+        <v>119.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>30036.6</v>
+        <v>3096.9</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>7221.07</v>
+        <v>75.67</v>
       </c>
       <c r="C7" t="n">
-        <v>555408</v>
+        <v>7056</v>
       </c>
       <c r="D7" t="n">
-        <v>278418.1</v>
+        <v>3537.07</v>
       </c>
       <c r="E7" t="n">
-        <v>5551.47</v>
+        <v>382.86</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1642.5</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>306.6</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21870</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8">
@@ -14655,22 +14649,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1436.49</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>110376</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>63828.86</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>662.3099999999999</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>955.5</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -14685,7 +14679,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7731.9</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="9">
@@ -14693,22 +14687,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>232.38</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>17136</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>10811.59</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>240.93</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>459</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14723,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3280.5</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -14731,25 +14725,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>185.22</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2067.12</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2723.4</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,13 +14763,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>62.55</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1779.03</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14784,7 +14778,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3030</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -14807,13 +14801,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>22.95</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>367.09</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14822,7 +14816,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>13.59</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1504.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,13 +14877,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1154.74</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14898,7 +14892,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2733.19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -15038,10 +15032,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15076,10 +15070,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15114,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>40763428.2</v>
+        <v>3559455.9</v>
       </c>
       <c r="C5" t="n">
-        <v>123004728</v>
+        <v>10077606</v>
       </c>
       <c r="D5" t="n">
-        <v>107158619.95</v>
+        <v>8779356.439999999</v>
       </c>
       <c r="E5" t="n">
-        <v>11924757.13</v>
+        <v>3383558.39</v>
       </c>
       <c r="F5" t="n">
-        <v>5833.38</v>
+        <v>5000.04</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1192140.18</v>
+        <v>104573.7</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>412454.7</v>
+        <v>93529.3</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>40729867.2</v>
+        <v>534916.8</v>
       </c>
       <c r="C6" t="n">
-        <v>70403256</v>
+        <v>2320164</v>
       </c>
       <c r="D6" t="n">
-        <v>57411407.92</v>
+        <v>1892013.09</v>
       </c>
       <c r="E6" t="n">
-        <v>2886359.11</v>
+        <v>476389.37</v>
       </c>
       <c r="F6" t="n">
-        <v>8333.4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>38073</v>
+        <v>693.75</v>
       </c>
       <c r="H6" t="n">
-        <v>217612.89</v>
+        <v>33115</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>29166.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>282944.77</v>
+        <v>29172.8</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>15886361.7</v>
+        <v>166468.5</v>
       </c>
       <c r="C7" t="n">
-        <v>30547440</v>
+        <v>388080</v>
       </c>
       <c r="D7" t="n">
-        <v>28212105.67</v>
+        <v>358411.51</v>
       </c>
       <c r="E7" t="n">
-        <v>1022802.83</v>
+        <v>70538.13</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>30386.25</v>
+        <v>83.25</v>
       </c>
       <c r="H7" t="n">
-        <v>84820.89</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>206015.4</v>
+        <v>3052.08</v>
       </c>
     </row>
     <row r="8">
@@ -15587,22 +15581,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3160278</v>
+        <v>5940</v>
       </c>
       <c r="C8" t="n">
-        <v>6070680</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>6467778.79</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>122023.99</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>17676.75</v>
+        <v>721.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15617,7 +15611,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>72834.5</v>
+        <v>601.9400000000001</v>
       </c>
     </row>
     <row r="9">
@@ -15625,22 +15619,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>511236</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>942480</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1095538.62</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>8491.5</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15655,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>30902.31</v>
+        <v>686.72</v>
       </c>
     </row>
     <row r="10">
@@ -15663,25 +15657,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>407484</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>166320</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>209461.27</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>6660</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>25654.43</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,13 +15695,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>137610</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138600</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>180269.11</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15716,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4995</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>28542.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>50490</v>
-      </c>
-      <c r="C12" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D12" t="n">
-        <v>37197.43</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>12151.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>29898</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1978.2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>13464</v>
-      </c>
-      <c r="C14" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D14" t="n">
-        <v>117009.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>7347.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>6336</v>
-      </c>
-      <c r="C15" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D15" t="n">
-        <v>276954.35</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>68820</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1413</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>594</v>
-      </c>
-      <c r="C16" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D16" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D19" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D20" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D24" t="n">
-        <v>200633.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5093.64</v>
-      </c>
-      <c r="C4" t="n">
-        <v>862344</v>
-      </c>
-      <c r="D4" t="n">
-        <v>677556</v>
-      </c>
-      <c r="E4" t="n">
-        <v>235800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13650</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3240</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>32400</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5983.47</v>
-      </c>
-      <c r="C5" t="n">
-        <v>594720</v>
-      </c>
-      <c r="D5" t="n">
-        <v>467280</v>
-      </c>
-      <c r="E5" t="n">
-        <v>108900</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9300</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>26460</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5193.63</v>
-      </c>
-      <c r="C6" t="n">
-        <v>318024</v>
-      </c>
-      <c r="D6" t="n">
-        <v>249876</v>
-      </c>
-      <c r="E6" t="n">
-        <v>54000</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5850</v>
-      </c>
-      <c r="H6" t="n">
-        <v>150</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>15450</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3727.17</v>
-      </c>
-      <c r="C7" t="n">
-        <v>176904</v>
-      </c>
-      <c r="D7" t="n">
-        <v>138996</v>
-      </c>
-      <c r="E7" t="n">
-        <v>18900</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3510</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>13350</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2566.35</v>
-      </c>
-      <c r="C8" t="n">
-        <v>59472</v>
-      </c>
-      <c r="D8" t="n">
-        <v>46728</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4950</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1704.96</v>
-      </c>
-      <c r="C9" t="n">
-        <v>28728</v>
-      </c>
-      <c r="D9" t="n">
-        <v>22572</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>330</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>886.14</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4356</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>527.9400000000001</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>397.8</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>368.19</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.31</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>792</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>239.94</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>26.64</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2692.56</v>
-      </c>
-      <c r="C5" t="n">
-        <v>327096</v>
-      </c>
-      <c r="D5" t="n">
-        <v>154669.68</v>
-      </c>
-      <c r="E5" t="n">
-        <v>12011.67</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>432</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5556.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4154.9</v>
-      </c>
-      <c r="C6" t="n">
-        <v>286221.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>126687.13</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9126</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5716.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3540.81</v>
-      </c>
-      <c r="C7" t="n">
-        <v>176904</v>
-      </c>
-      <c r="D7" t="n">
-        <v>88679.45</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4020.03</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>526.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8010</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2566.35</v>
-      </c>
-      <c r="C8" t="n">
-        <v>59472</v>
-      </c>
-      <c r="D8" t="n">
-        <v>34391.81</v>
-      </c>
-      <c r="E8" t="n">
-        <v>662.3099999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1443</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3514.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1704.96</v>
-      </c>
-      <c r="C9" t="n">
-        <v>28728</v>
-      </c>
-      <c r="D9" t="n">
-        <v>18125.32</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>280.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>801.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>886.14</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3789.72</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>186.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>527.9400000000001</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2490.64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>397.8</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1101.28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>368.19</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1504.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.31</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>769.8200000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>239.94</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>26.64</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5923635.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>17990280</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15672678.67</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2213030.08</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4166.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>119512.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>52343.17</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>9140788.800000001</v>
-      </c>
-      <c r="C6" t="n">
-        <v>15742188</v>
-      </c>
-      <c r="D6" t="n">
-        <v>12837207.09</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1681374.24</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5411.25</v>
-      </c>
-      <c r="H6" t="n">
-        <v>23653.57</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>53849.43</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7789785.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9729720</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8985888.470000001</v>
-      </c>
-      <c r="E7" t="n">
-        <v>740650.33</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9740.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>75454.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5645970</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3270960</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3484921.9</v>
-      </c>
-      <c r="E8" t="n">
-        <v>122023.99</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>26695.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>33106.59</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3750912</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1580040</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1836638.27</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5189.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7553.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1949508</v>
-      </c>
-      <c r="C10" t="n">
-        <v>304920</v>
-      </c>
-      <c r="D10" t="n">
-        <v>384012.33</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1760.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1161468</v>
-      </c>
-      <c r="C11" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D11" t="n">
-        <v>252376.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>875160</v>
-      </c>
-      <c r="C12" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D12" t="n">
-        <v>111592.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>810018</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1080882</v>
-      </c>
-      <c r="C14" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78006.27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>527868</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>94446</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>58608</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>16856.46</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1824480</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1433520</v>
-      </c>
-      <c r="E4" t="n">
-        <v>732600</v>
-      </c>
-      <c r="F4" t="n">
-        <v>27</v>
-      </c>
-      <c r="G4" t="n">
-        <v>50160</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3990</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>177000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3595.41</v>
-      </c>
-      <c r="C5" t="n">
-        <v>333144</v>
-      </c>
-      <c r="D5" t="n">
-        <v>261756</v>
-      </c>
-      <c r="E5" t="n">
-        <v>166500</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10050</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>47280</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>303.93</v>
-      </c>
-      <c r="C6" t="n">
-        <v>46872</v>
-      </c>
-      <c r="D6" t="n">
-        <v>36828</v>
-      </c>
-      <c r="E6" t="n">
-        <v>15300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>750</v>
-      </c>
-      <c r="H6" t="n">
-        <v>210</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8370</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>79.65000000000001</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7056</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5544</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1617.93</v>
-      </c>
-      <c r="C5" t="n">
-        <v>183229.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>86641.24000000001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>18364.95</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>378</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9928.799999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>243.14</v>
-      </c>
-      <c r="C6" t="n">
-        <v>42184.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>18671.8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2585.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3096.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>75.67</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7056</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3537.07</v>
-      </c>
-      <c r="E7" t="n">
-        <v>382.86</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>63.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>72.90000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
+        <v>282.6</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3559455.9</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10077606</v>
-      </c>
-      <c r="D5" t="n">
-        <v>8779356.439999999</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3383558.39</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000.04</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>104573.7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>93529.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>534916.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2320164</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1892013.09</v>
-      </c>
-      <c r="E6" t="n">
-        <v>476389.37</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>693.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>33115</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>29172.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>166468.5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>388080</v>
-      </c>
-      <c r="D7" t="n">
-        <v>358411.51</v>
-      </c>
-      <c r="E7" t="n">
-        <v>70538.13</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3052.08</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5940</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>721.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>601.9400000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>686.72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>282.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
@@ -538,7 +538,7 @@
         <v>63450</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>33</v>
@@ -576,7 +576,7 @@
         <v>40470</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>18</v>
@@ -614,7 +614,7 @@
         <v>6840</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -652,7 +652,7 @@
         <v>1080</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -1546,7 +1546,7 @@
         <v>3600</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>2052</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>567685.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>10890</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>8</v>
@@ -9896,7 +9896,7 @@
         <v>11970</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -9934,7 +9934,7 @@
         <v>1380</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -9972,7 +9972,7 @@
         <v>420</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -10828,7 +10828,7 @@
         <v>14569.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>5.4</v>
@@ -10866,7 +10866,7 @@
         <v>3898.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
@@ -10904,7 +10904,7 @@
         <v>788.4</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>3.5</v>
@@ -11760,7 +11760,7 @@
         <v>4309.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
@@ -11798,7 +11798,7 @@
         <v>786.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>0.5</v>
@@ -11836,7 +11836,7 @@
         <v>306.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>1.4</v>
@@ -12692,7 +12692,7 @@
         <v>1192140.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>114999</v>
       </c>
       <c r="J5" t="n">
         <v>122499.3</v>
@@ -12730,7 +12730,7 @@
         <v>217612.89</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>29166.5</v>
@@ -12768,7 +12768,7 @@
         <v>84820.89</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>81666.2</v>
@@ -13586,7 +13586,7 @@
         <v>3990</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -16420,7 +16420,7 @@
         <v>4030569.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>114999</v>
       </c>
       <c r="J5" t="n">
         <v>314998.2</v>
@@ -16458,7 +16458,7 @@
         <v>1078603.02</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>268331</v>
       </c>
       <c r="J6" t="n">
         <v>87499.5</v>
@@ -16496,7 +16496,7 @@
         <v>218110.86</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>204165.5</v>
@@ -17314,7 +17314,7 @@
         <v>6090</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
@@ -20110,7 +20110,7 @@
         <v>28470</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>

--- a/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
@@ -544,7 +544,7 @@
         <v>33</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>913</v>
       </c>
       <c r="L4" t="n">
         <v>1291260</v>
@@ -582,7 +582,7 @@
         <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="L5" t="n">
         <v>769740</v>
@@ -620,7 +620,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="L6" t="n">
         <v>347220</v>
@@ -658,7 +658,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="L7" t="n">
         <v>178380</v>
@@ -696,7 +696,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="L8" t="n">
         <v>82020</v>
@@ -734,7 +734,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
         <v>29520</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
         <v>14250</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>690</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>1470</v>
@@ -1476,7 +1476,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L4" t="n">
         <v>104490</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="L5" t="n">
         <v>93360</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
         <v>45150</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>19560</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>8580</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2160</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>4260</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>21.84</v>
       </c>
       <c r="L5" t="n">
         <v>19605.6</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>18.85</v>
       </c>
       <c r="L6" t="n">
         <v>16705.5</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>11736</v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>6091.8</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>1749.6</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>3791.4</v>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>465934.56</v>
       </c>
       <c r="L5" t="n">
         <v>184684.75</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>402145.9</v>
       </c>
       <c r="L6" t="n">
         <v>157365.81</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>174938.8</v>
       </c>
       <c r="L7" t="n">
         <v>110553.12</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>76802.39999999999</v>
       </c>
       <c r="L8" t="n">
         <v>57384.76</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L9" t="n">
         <v>16481.23</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L10" t="n">
         <v>35714.99</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
         <v>85680</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
         <v>25050</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>6270</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="L5" t="n">
         <v>5260.5</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>2319.9</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>107523.36</v>
       </c>
       <c r="L5" t="n">
         <v>49553.91</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>21853.46</v>
@@ -7068,7 +7068,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
         <v>27270</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>8190</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>1380</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>30</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="L5" t="n">
         <v>1719.9</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
         <v>510.6</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>44801.4</v>
       </c>
       <c r="L5" t="n">
         <v>16201.46</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>27734.2</v>
       </c>
       <c r="L6" t="n">
         <v>4809.85</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34987.76</v>
       </c>
       <c r="L7" t="n">
         <v>169.56</v>
@@ -9864,7 +9864,7 @@
         <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="L4" t="n">
         <v>264180</v>
@@ -9902,7 +9902,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="L5" t="n">
         <v>208500</v>
@@ -9940,7 +9940,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L6" t="n">
         <v>81180</v>
@@ -9978,7 +9978,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L7" t="n">
         <v>36450</v>
@@ -10016,7 +10016,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>10890</v>
@@ -10054,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>4050</v>
@@ -10244,7 +10244,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>780</v>
@@ -10834,7 +10834,7 @@
         <v>5.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>261.24</v>
       </c>
       <c r="L5" t="n">
         <v>161645.4</v>
@@ -10872,7 +10872,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>172.25</v>
       </c>
       <c r="L6" t="n">
         <v>128471.4</v>
@@ -10910,7 +10910,7 @@
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>105.78</v>
       </c>
       <c r="L7" t="n">
         <v>107028</v>
@@ -10948,7 +10948,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="L8" t="n">
         <v>58234.2</v>
@@ -10986,7 +10986,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
         <v>23911.2</v>
@@ -11024,7 +11024,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
         <v>12682.5</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>690</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>1470</v>
@@ -11766,7 +11766,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>43785</v>
@@ -11804,7 +11804,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>54.6</v>
       </c>
       <c r="L6" t="n">
         <v>30036.6</v>
@@ -11842,7 +11842,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>19.68</v>
       </c>
       <c r="L7" t="n">
         <v>21870</v>
@@ -11880,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="L8" t="n">
         <v>7731.9</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>3280.5</v>
@@ -12108,7 +12108,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>780</v>
@@ -12698,7 +12698,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1908539.64</v>
       </c>
       <c r="L5" t="n">
         <v>412454.7</v>
@@ -12736,7 +12736,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1164836.4</v>
       </c>
       <c r="L6" t="n">
         <v>282944.77</v>
@@ -12774,7 +12774,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>419853.12</v>
       </c>
       <c r="L7" t="n">
         <v>206015.4</v>
@@ -12812,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>153604.8</v>
       </c>
       <c r="L8" t="n">
         <v>72834.5</v>
@@ -12850,7 +12850,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L9" t="n">
         <v>30902.31</v>
@@ -13040,7 +13040,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L14" t="n">
         <v>7347.6</v>
@@ -13592,7 +13592,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L4" t="n">
         <v>177000</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>47280</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="L5" t="n">
         <v>9928.799999999999</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>134404.2</v>
       </c>
       <c r="L5" t="n">
         <v>93529.3</v>
@@ -16426,7 +16426,7 @@
         <v>314998.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5573294.16</v>
       </c>
       <c r="L5" t="n">
         <v>1522699.67</v>
@@ -16464,7 +16464,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3674781.5</v>
       </c>
       <c r="L6" t="n">
         <v>1210200.59</v>
@@ -16502,7 +16502,7 @@
         <v>204165.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2256710.52</v>
       </c>
       <c r="L7" t="n">
         <v>1008203.76</v>
@@ -16540,7 +16540,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1497646.8</v>
       </c>
       <c r="L8" t="n">
         <v>548566.16</v>
@@ -16578,7 +16578,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>597352</v>
       </c>
       <c r="L9" t="n">
         <v>225243.5</v>
@@ -16616,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>149338</v>
       </c>
       <c r="L10" t="n">
         <v>119469.15</v>
@@ -16730,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L13" t="n">
         <v>6499.8</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L14" t="n">
         <v>13847.4</v>
@@ -17320,7 +17320,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="L4" t="n">
         <v>261000</v>
@@ -17358,7 +17358,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="L5" t="n">
         <v>215790</v>
@@ -17396,7 +17396,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="L6" t="n">
         <v>142080</v>
@@ -17434,7 +17434,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L7" t="n">
         <v>94320</v>
@@ -17472,7 +17472,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L8" t="n">
         <v>52290</v>
@@ -17510,7 +17510,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
         <v>20280</v>
@@ -17548,7 +17548,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>5730</v>
@@ -17662,7 +17662,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>210</v>
@@ -18290,7 +18290,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>45315.9</v>
@@ -18328,7 +18328,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>89.7</v>
       </c>
       <c r="L6" t="n">
         <v>52569.6</v>
@@ -18366,7 +18366,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>75.44</v>
       </c>
       <c r="L7" t="n">
         <v>56592</v>
@@ -18404,7 +18404,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>58.5</v>
       </c>
       <c r="L8" t="n">
         <v>37125.9</v>
@@ -18442,7 +18442,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
         <v>16426.8</v>
@@ -18480,7 +18480,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>5099.7</v>
@@ -18594,7 +18594,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>210</v>
@@ -19222,7 +19222,7 @@
         <v>87499.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1980221.88</v>
       </c>
       <c r="L5" t="n">
         <v>426875.78</v>
@@ -19260,7 +19260,7 @@
         <v>58333</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1913659.8</v>
       </c>
       <c r="L6" t="n">
         <v>495205.63</v>
@@ -19298,7 +19298,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1609436.96</v>
       </c>
       <c r="L7" t="n">
         <v>533096.64</v>
@@ -19336,7 +19336,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1248039</v>
       </c>
       <c r="L8" t="n">
         <v>349725.98</v>
@@ -19374,7 +19374,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>512016</v>
       </c>
       <c r="L9" t="n">
         <v>154740.46</v>
@@ -19412,7 +19412,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>128004</v>
       </c>
       <c r="L10" t="n">
         <v>48039.17</v>
@@ -19526,7 +19526,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L13" t="n">
         <v>1978.2</v>
@@ -20116,7 +20116,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L4" t="n">
         <v>311070</v>
@@ -20154,7 +20154,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
         <v>116400</v>
@@ -20192,7 +20192,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>26160</v>
@@ -20230,7 +20230,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>5160</v>
@@ -21086,7 +21086,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L5" t="n">
         <v>24444</v>
@@ -21124,7 +21124,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="L6" t="n">
         <v>9679.200000000001</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>3096</v>
@@ -22018,7 +22018,7 @@
         <v>104999.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>896028</v>
       </c>
       <c r="L5" t="n">
         <v>230262.48</v>
@@ -22056,7 +22056,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>124803.9</v>
       </c>
       <c r="L6" t="n">
         <v>91178.06</v>
@@ -22094,7 +22094,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>29164.32</v>

--- a/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>153792.36</v>
+        <v>153702.36</v>
       </c>
       <c r="C4" t="n">
         <v>27725040</v>
@@ -532,7 +537,7 @@
         <v>125</v>
       </c>
       <c r="G4" t="n">
-        <v>479520</v>
+        <v>477180</v>
       </c>
       <c r="H4" t="n">
         <v>63450</v>
@@ -544,10 +549,13 @@
         <v>33</v>
       </c>
       <c r="K4" t="n">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="L4" t="n">
-        <v>1291260</v>
+        <v>1288470</v>
+      </c>
+      <c r="M4" t="n">
+        <v>59940</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>112077.9</v>
+        <v>112043.97</v>
       </c>
       <c r="C5" t="n">
         <v>14372064</v>
@@ -570,7 +578,7 @@
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>316230</v>
+        <v>315360</v>
       </c>
       <c r="H5" t="n">
         <v>40470</v>
@@ -582,10 +590,13 @@
         <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="L5" t="n">
-        <v>769740</v>
+        <v>768210</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30570</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>68585.67</v>
+        <v>68584.05</v>
       </c>
       <c r="C6" t="n">
         <v>5919984</v>
@@ -608,7 +619,7 @@
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>166800</v>
+        <v>166170</v>
       </c>
       <c r="H6" t="n">
         <v>6840</v>
@@ -620,10 +631,13 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L6" t="n">
-        <v>347220</v>
+        <v>346440</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14220</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>37144.17</v>
+        <v>37143.72</v>
       </c>
       <c r="C7" t="n">
         <v>2825928</v>
@@ -646,7 +660,7 @@
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>70440</v>
+        <v>69990</v>
       </c>
       <c r="H7" t="n">
         <v>1080</v>
@@ -661,7 +675,10 @@
         <v>129</v>
       </c>
       <c r="L7" t="n">
-        <v>178380</v>
+        <v>177360</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9030</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +686,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>20211.39</v>
+        <v>20211.21</v>
       </c>
       <c r="C8" t="n">
         <v>1115856</v>
@@ -684,7 +701,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>30720</v>
+        <v>30270</v>
       </c>
       <c r="H8" t="n">
         <v>180</v>
@@ -699,7 +716,10 @@
         <v>78</v>
       </c>
       <c r="L8" t="n">
-        <v>82020</v>
+        <v>81330</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4710</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +727,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>11172.6</v>
+        <v>11172.33</v>
       </c>
       <c r="C9" t="n">
         <v>407736</v>
@@ -722,7 +742,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>18780</v>
+        <v>18450</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -737,7 +757,10 @@
         <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>29520</v>
+        <v>29160</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3510</v>
       </c>
     </row>
     <row r="10">
@@ -775,7 +798,10 @@
         <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>14250</v>
+        <v>14160</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4140</v>
       </c>
     </row>
     <row r="11">
@@ -813,7 +839,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6330</v>
+        <v>6030</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="12">
@@ -851,7 +880,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3060</v>
+        <v>2880</v>
+      </c>
+      <c r="M12" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="13">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>690</v>
       </c>
+      <c r="M13" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>1470</v>
       </c>
+      <c r="M14" t="n">
+        <v>840</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>210</v>
       </c>
+      <c r="M15" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>60</v>
       </c>
+      <c r="M16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1464,7 +1541,7 @@
         <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>35040</v>
+        <v>35160</v>
       </c>
       <c r="H4" t="n">
         <v>4950</v>
@@ -1479,7 +1556,10 @@
         <v>45</v>
       </c>
       <c r="L4" t="n">
-        <v>104490</v>
+        <v>104790</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10710</v>
       </c>
     </row>
     <row r="5">
@@ -1487,7 +1567,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>8009.19</v>
+        <v>8009.1</v>
       </c>
       <c r="C5" t="n">
         <v>791280</v>
@@ -1517,7 +1597,10 @@
         <v>52</v>
       </c>
       <c r="L5" t="n">
-        <v>93360</v>
+        <v>93420</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9750</v>
       </c>
     </row>
     <row r="6">
@@ -1540,7 +1623,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>21840</v>
+        <v>21870</v>
       </c>
       <c r="H6" t="n">
         <v>3600</v>
@@ -1555,7 +1638,10 @@
         <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>45150</v>
+        <v>45180</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3450</v>
       </c>
     </row>
     <row r="7">
@@ -1593,7 +1679,10 @@
         <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>19560</v>
+        <v>19620</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2040</v>
       </c>
     </row>
     <row r="8">
@@ -1633,6 +1722,9 @@
       <c r="L8" t="n">
         <v>8580</v>
       </c>
+      <c r="M8" t="n">
+        <v>900</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1671,6 +1763,9 @@
       <c r="L9" t="n">
         <v>2160</v>
       </c>
+      <c r="M9" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1804,9 @@
       <c r="L10" t="n">
         <v>4260</v>
       </c>
+      <c r="M10" t="n">
+        <v>2940</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,7 +1843,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>750</v>
+        <v>780</v>
+      </c>
+      <c r="M11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -1785,6 +1886,9 @@
       <c r="L12" t="n">
         <v>810</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1823,6 +1927,9 @@
       <c r="L13" t="n">
         <v>120</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1861,6 +1968,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3604.14</v>
+        <v>3604.1</v>
       </c>
       <c r="C5" t="n">
         <v>435204</v>
@@ -2446,10 +2598,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>21.84</v>
+        <v>17.21</v>
       </c>
       <c r="L5" t="n">
-        <v>19605.6</v>
+        <v>19618.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="6">
@@ -2472,22 +2627,25 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1092</v>
+        <v>1093.5</v>
       </c>
       <c r="H6" t="n">
         <v>2052</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>18.85</v>
+        <v>14.7</v>
       </c>
       <c r="L6" t="n">
-        <v>16705.5</v>
+        <v>16716.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="7">
@@ -2522,10 +2680,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.38</v>
       </c>
       <c r="L7" t="n">
-        <v>11736</v>
+        <v>11772</v>
+      </c>
+      <c r="M7" t="n">
+        <v>714</v>
       </c>
     </row>
     <row r="8">
@@ -2560,10 +2721,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="L8" t="n">
         <v>6091.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>540</v>
       </c>
     </row>
     <row r="9">
@@ -2598,10 +2762,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>1749.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -2636,10 +2803,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="L10" t="n">
         <v>3791.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2940</v>
       </c>
     </row>
     <row r="11">
@@ -2677,7 +2847,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>750</v>
+        <v>780</v>
+      </c>
+      <c r="M11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -2717,6 +2890,9 @@
       <c r="L12" t="n">
         <v>810</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2755,6 +2931,9 @@
       <c r="L13" t="n">
         <v>120</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2793,6 +2972,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2831,6 +3013,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,16 +3575,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>7929098.1</v>
+        <v>7929009</v>
       </c>
       <c r="C5" t="n">
-        <v>23936220</v>
+        <v>18278568</v>
       </c>
       <c r="D5" t="n">
-        <v>20852631.8</v>
+        <v>39511549.44</v>
       </c>
       <c r="E5" t="n">
-        <v>4535797.19</v>
+        <v>8493541.199999999</v>
       </c>
       <c r="F5" t="n">
         <v>8333.4</v>
@@ -3369,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>277867.26</v>
+        <v>5725080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3378,10 +3602,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>465934.56</v>
+        <v>835745.87</v>
       </c>
       <c r="L5" t="n">
-        <v>184684.75</v>
+        <v>3531276</v>
+      </c>
+      <c r="M5" t="n">
+        <v>58500</v>
       </c>
     </row>
     <row r="6">
@@ -3392,34 +3619,37 @@
         <v>11883801.6</v>
       </c>
       <c r="C6" t="n">
-        <v>21305592</v>
+        <v>16269724.8</v>
       </c>
       <c r="D6" t="n">
-        <v>17373969.65</v>
+        <v>32920183.3</v>
       </c>
       <c r="E6" t="n">
-        <v>3446817.19</v>
+        <v>6454363.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>20202</v>
+        <v>59049</v>
       </c>
       <c r="H6" t="n">
-        <v>567685.8</v>
+        <v>11696400</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>402145.9</v>
+        <v>713918.87</v>
       </c>
       <c r="L6" t="n">
-        <v>157365.81</v>
+        <v>3008988</v>
+      </c>
+      <c r="M6" t="n">
+        <v>82800</v>
       </c>
     </row>
     <row r="7">
@@ -3430,22 +3660,22 @@
         <v>9171191.699999999</v>
       </c>
       <c r="C7" t="n">
-        <v>13804560</v>
+        <v>10541664</v>
       </c>
       <c r="D7" t="n">
-        <v>12749209.28</v>
+        <v>24157191.17</v>
       </c>
       <c r="E7" t="n">
-        <v>2292489.11</v>
+        <v>4292817.75</v>
       </c>
       <c r="F7" t="n">
         <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>20562.75</v>
+        <v>60021</v>
       </c>
       <c r="H7" t="n">
-        <v>48469.08</v>
+        <v>998640</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3454,10 +3684,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>174938.8</v>
+        <v>309787.28</v>
       </c>
       <c r="L7" t="n">
-        <v>110553.12</v>
+        <v>2118960</v>
+      </c>
+      <c r="M7" t="n">
+        <v>214200</v>
       </c>
     </row>
     <row r="8">
@@ -3468,22 +3701,22 @@
         <v>6290064</v>
       </c>
       <c r="C8" t="n">
-        <v>5072760</v>
+        <v>3873744</v>
       </c>
       <c r="D8" t="n">
-        <v>5404582.28</v>
+        <v>10240598.02</v>
       </c>
       <c r="E8" t="n">
-        <v>569445.3100000001</v>
+        <v>1066319.1</v>
       </c>
       <c r="F8" t="n">
         <v>79167.3</v>
       </c>
       <c r="G8" t="n">
-        <v>91630.5</v>
+        <v>267462</v>
       </c>
       <c r="H8" t="n">
-        <v>21163.72</v>
+        <v>436050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3492,10 +3725,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>76802.39999999999</v>
+        <v>142948.86</v>
       </c>
       <c r="L8" t="n">
-        <v>57384.76</v>
+        <v>1096524</v>
+      </c>
+      <c r="M8" t="n">
+        <v>162000</v>
       </c>
     </row>
     <row r="9">
@@ -3506,22 +3742,22 @@
         <v>2459160</v>
       </c>
       <c r="C9" t="n">
-        <v>1275120</v>
+        <v>973728</v>
       </c>
       <c r="D9" t="n">
-        <v>1482199.31</v>
+        <v>2808470.02</v>
       </c>
       <c r="E9" t="n">
-        <v>88777.89</v>
+        <v>166241.7</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>21700.5</v>
+        <v>63342</v>
       </c>
       <c r="H9" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3530,10 +3766,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>42668</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>16481.23</v>
+        <v>314928</v>
+      </c>
+      <c r="M9" t="n">
+        <v>99000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,22 +3783,22 @@
         <v>1146222</v>
       </c>
       <c r="C10" t="n">
-        <v>1469160</v>
+        <v>1121904</v>
       </c>
       <c r="D10" t="n">
-        <v>1850241.21</v>
+        <v>3505835.52</v>
       </c>
       <c r="E10" t="n">
-        <v>144259.92</v>
+        <v>270135</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5550</v>
+        <v>16200</v>
       </c>
       <c r="H10" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3568,10 +3807,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>21334</v>
+        <v>42243.72</v>
       </c>
       <c r="L10" t="n">
-        <v>35714.99</v>
+        <v>682452</v>
+      </c>
+      <c r="M10" t="n">
+        <v>882000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,10 +3824,10 @@
         <v>661914</v>
       </c>
       <c r="C11" t="n">
-        <v>471240</v>
+        <v>359856</v>
       </c>
       <c r="D11" t="n">
-        <v>612914.97</v>
+        <v>1161350.78</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3594,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3609,7 +3851,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7065</v>
+        <v>140400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="12">
@@ -3620,10 +3865,10 @@
         <v>574596</v>
       </c>
       <c r="C12" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D12" t="n">
-        <v>297579.46</v>
+        <v>563853.3100000001</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -3632,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -3647,7 +3892,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>7630.2</v>
+        <v>145800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3658,10 +3906,10 @@
         <v>640728</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3673,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3685,7 +3933,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1130.4</v>
+        <v>21600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3696,10 +3947,10 @@
         <v>704682</v>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D14" t="n">
-        <v>156012.53</v>
+        <v>295612.42</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3723,6 +3974,9 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3734,10 +3988,10 @@
         <v>275814</v>
       </c>
       <c r="C15" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D15" t="n">
-        <v>79129.81</v>
+        <v>149935.1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3761,6 +4015,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3772,10 +4029,10 @@
         <v>212058</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3799,6 +4056,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3839,6 +4099,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3877,6 +4140,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3915,6 +4181,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>26250</v>
+        <v>26310</v>
       </c>
       <c r="H4" t="n">
         <v>1560</v>
@@ -4275,7 +4568,10 @@
         <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>85680</v>
+        <v>86220</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4313,7 +4609,10 @@
         <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>25050</v>
+        <v>25230</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4353,6 +4652,9 @@
       <c r="L6" t="n">
         <v>6270</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>1260</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>210</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>150</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5.04</v>
+        <v>3.97</v>
       </c>
       <c r="L5" t="n">
-        <v>5260.5</v>
+        <v>5298.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>2319.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5323,6 +5697,9 @@
       <c r="L7" t="n">
         <v>756</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>149.1</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>121.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>1800711</v>
       </c>
       <c r="C5" t="n">
-        <v>9132354</v>
+        <v>6973797.6</v>
       </c>
       <c r="D5" t="n">
-        <v>7955876.72</v>
+        <v>15074788.61</v>
       </c>
       <c r="E5" t="n">
-        <v>2103293.05</v>
+        <v>3938537.25</v>
       </c>
       <c r="F5" t="n">
         <v>833.34</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>44817.3</v>
+        <v>923400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>107523.36</v>
+        <v>192864.43</v>
       </c>
       <c r="L5" t="n">
-        <v>49553.91</v>
+        <v>953694</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,22 +6631,22 @@
         <v>182793.6</v>
       </c>
       <c r="C6" t="n">
-        <v>3941784</v>
+        <v>3010089.6</v>
       </c>
       <c r="D6" t="n">
-        <v>3214387.83</v>
+        <v>6090619.39</v>
       </c>
       <c r="E6" t="n">
-        <v>1345099.39</v>
+        <v>2518776</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1332</v>
+        <v>3888</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>21853.46</v>
+        <v>417582</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,19 +6672,19 @@
         <v>59627.7</v>
       </c>
       <c r="C7" t="n">
-        <v>304920</v>
+        <v>232848</v>
       </c>
       <c r="D7" t="n">
-        <v>281609.04</v>
+        <v>533592.58</v>
       </c>
       <c r="E7" t="n">
-        <v>35269.06</v>
+        <v>66043.35000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>582.75</v>
+        <v>1701</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6253,7 +6699,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7121.52</v>
+        <v>136080</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6264,10 +6713,10 @@
         <v>33660</v>
       </c>
       <c r="C8" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D8" t="n">
-        <v>59066.47</v>
+        <v>111919.1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2164.5</v>
+        <v>6318</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,7 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1404.52</v>
+        <v>26838</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6302,13 +6754,13 @@
         <v>19008</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>183161.09</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6329,7 +6781,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1144.53</v>
+        <v>21870</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7056,7 +7565,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>24000</v>
+        <v>24060</v>
       </c>
       <c r="H4" t="n">
         <v>3240</v>
@@ -7071,7 +7580,10 @@
         <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>27270</v>
+        <v>27300</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7111,6 +7623,9 @@
       <c r="L5" t="n">
         <v>8190</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>1380</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>30</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="L5" t="n">
         <v>1719.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>510.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8157,6 +8750,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>1195811.1</v>
       </c>
       <c r="C5" t="n">
-        <v>3567564</v>
+        <v>2724321.6</v>
       </c>
       <c r="D5" t="n">
-        <v>3107971.87</v>
+        <v>5888982.53</v>
       </c>
       <c r="E5" t="n">
-        <v>91447.52</v>
+        <v>171240.75</v>
       </c>
       <c r="F5" t="n">
         <v>1666.68</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>188232.66</v>
+        <v>3878280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>44801.4</v>
+        <v>80360.17999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>16201.46</v>
+        <v>309582</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +9643,22 @@
         <v>402969.6</v>
       </c>
       <c r="C6" t="n">
-        <v>1372140</v>
+        <v>1047816</v>
       </c>
       <c r="D6" t="n">
-        <v>1118932.47</v>
+        <v>2120152.32</v>
       </c>
       <c r="E6" t="n">
-        <v>112091.62</v>
+        <v>209898</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1637.25</v>
+        <v>4779</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>27734.2</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>4809.85</v>
+        <v>91908</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9022,10 +9684,10 @@
         <v>75804.3</v>
       </c>
       <c r="C7" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D7" t="n">
-        <v>102403.29</v>
+        <v>194033.66</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -9034,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1165.5</v>
+        <v>3402</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>34987.76</v>
+        <v>61957.46</v>
       </c>
       <c r="L7" t="n">
-        <v>169.56</v>
+        <v>3240</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,10 +9725,10 @@
         <v>13068</v>
       </c>
       <c r="C8" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D8" t="n">
-        <v>29533.24</v>
+        <v>55959.55</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -9087,6 +9752,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,10 +10577,10 @@
         <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>101340</v>
+        <v>101370</v>
       </c>
       <c r="H4" t="n">
-        <v>10890</v>
+        <v>10770</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -9867,7 +10592,10 @@
         <v>263</v>
       </c>
       <c r="L4" t="n">
-        <v>264180</v>
+        <v>264330</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17760</v>
       </c>
     </row>
     <row r="5">
@@ -9890,7 +10618,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>97560</v>
+        <v>97650</v>
       </c>
       <c r="H5" t="n">
         <v>11970</v>
@@ -9905,7 +10633,10 @@
         <v>213</v>
       </c>
       <c r="L5" t="n">
-        <v>208500</v>
+        <v>208650</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10530</v>
       </c>
     </row>
     <row r="6">
@@ -9928,7 +10659,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>41160</v>
+        <v>41250</v>
       </c>
       <c r="H6" t="n">
         <v>1380</v>
@@ -9940,10 +10671,13 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L6" t="n">
-        <v>81180</v>
+        <v>81210</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4200</v>
       </c>
     </row>
     <row r="7">
@@ -9983,6 +10717,9 @@
       <c r="L7" t="n">
         <v>36450</v>
       </c>
+      <c r="M7" t="n">
+        <v>2370</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -10021,6 +10758,9 @@
       <c r="L8" t="n">
         <v>10890</v>
       </c>
+      <c r="M8" t="n">
+        <v>1050</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10059,6 +10799,9 @@
       <c r="L9" t="n">
         <v>4050</v>
       </c>
+      <c r="M9" t="n">
+        <v>480</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>3060</v>
       </c>
+      <c r="M10" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>3030</v>
       </c>
+      <c r="M11" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>1290</v>
       </c>
+      <c r="M12" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>210</v>
       </c>
+      <c r="M13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>780</v>
       </c>
+      <c r="M14" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>150</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>50435.06</v>
+        <v>50419.79</v>
       </c>
       <c r="C5" t="n">
         <v>7904635.2</v>
@@ -10828,16 +11628,19 @@
         <v>14569.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="J5" t="n">
         <v>5.4</v>
       </c>
       <c r="K5" t="n">
-        <v>261.24</v>
+        <v>202.9</v>
       </c>
       <c r="L5" t="n">
-        <v>161645.4</v>
+        <v>161324.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>611.4</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>54868.54</v>
+        <v>54867.24</v>
       </c>
       <c r="C6" t="n">
         <v>5327985.6</v>
@@ -10860,22 +11663,25 @@
         <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>8340</v>
+        <v>8308.5</v>
       </c>
       <c r="H6" t="n">
         <v>3898.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>172.25</v>
+        <v>133.85</v>
       </c>
       <c r="L6" t="n">
-        <v>128471.4</v>
+        <v>128182.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1137.6</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>35286.96</v>
+        <v>35286.53</v>
       </c>
       <c r="C7" t="n">
         <v>2825928</v>
@@ -10898,22 +11704,25 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>10566</v>
+        <v>10498.5</v>
       </c>
       <c r="H7" t="n">
         <v>788.4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="J7" t="n">
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>105.78</v>
+        <v>82.3</v>
       </c>
       <c r="L7" t="n">
-        <v>107028</v>
+        <v>106416</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3160.5</v>
       </c>
     </row>
     <row r="8">
@@ -10921,7 +11730,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>20211.39</v>
+        <v>20211.21</v>
       </c>
       <c r="C8" t="n">
         <v>1115856</v>
@@ -10936,7 +11745,7 @@
         <v>5.7</v>
       </c>
       <c r="G8" t="n">
-        <v>19968</v>
+        <v>19675.5</v>
       </c>
       <c r="H8" t="n">
         <v>153</v>
@@ -10948,10 +11757,13 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>70.2</v>
+        <v>57.41</v>
       </c>
       <c r="L8" t="n">
-        <v>58234.2</v>
+        <v>57744.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2826</v>
       </c>
     </row>
     <row r="9">
@@ -10959,7 +11771,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>11172.6</v>
+        <v>11172.33</v>
       </c>
       <c r="C9" t="n">
         <v>407736</v>
@@ -10974,7 +11786,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>15963</v>
+        <v>15682.5</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -10986,10 +11798,13 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>22.48</v>
       </c>
       <c r="L9" t="n">
-        <v>23911.2</v>
+        <v>23619.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3510</v>
       </c>
     </row>
     <row r="10">
@@ -11024,10 +11839,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>6.09</v>
       </c>
       <c r="L10" t="n">
-        <v>12682.5</v>
+        <v>12602.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4140</v>
       </c>
     </row>
     <row r="11">
@@ -11065,7 +11883,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6330</v>
+        <v>6030</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="12">
@@ -11103,7 +11924,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3060</v>
+        <v>2880</v>
+      </c>
+      <c r="M12" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="13">
@@ -11138,10 +11962,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>690</v>
+      </c>
+      <c r="M13" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -11176,10 +12003,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>1470</v>
+      </c>
+      <c r="M14" t="n">
+        <v>840</v>
       </c>
     </row>
     <row r="15">
@@ -11219,6 +12049,9 @@
       <c r="L15" t="n">
         <v>210</v>
       </c>
+      <c r="M15" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>60</v>
       </c>
+      <c r="M16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11760,16 +12632,19 @@
         <v>4309.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>89.45999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="L5" t="n">
-        <v>43785</v>
+        <v>43816.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>210.6</v>
       </c>
     </row>
     <row r="6">
@@ -11792,22 +12667,25 @@
         <v>0.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2058</v>
+        <v>2062.5</v>
       </c>
       <c r="H6" t="n">
         <v>786.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>54.6</v>
+        <v>43.1</v>
       </c>
       <c r="L6" t="n">
-        <v>30036.6</v>
+        <v>30047.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>336</v>
       </c>
     </row>
     <row r="7">
@@ -11836,16 +12714,19 @@
         <v>306.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="J7" t="n">
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>19.68</v>
+        <v>15.31</v>
       </c>
       <c r="L7" t="n">
         <v>21870</v>
+      </c>
+      <c r="M7" t="n">
+        <v>829.5</v>
       </c>
     </row>
     <row r="8">
@@ -11880,10 +12761,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7.2</v>
+        <v>5.89</v>
       </c>
       <c r="L8" t="n">
         <v>7731.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>630</v>
       </c>
     </row>
     <row r="9">
@@ -11918,10 +12802,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L9" t="n">
         <v>3280.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="10">
@@ -11961,6 +12848,9 @@
       <c r="L10" t="n">
         <v>2723.4</v>
       </c>
+      <c r="M10" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11999,6 +12889,9 @@
       <c r="L11" t="n">
         <v>3030</v>
       </c>
+      <c r="M11" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>1290</v>
       </c>
+      <c r="M12" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>210</v>
       </c>
+      <c r="M13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12108,10 +13007,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>780</v>
+      </c>
+      <c r="M14" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="15">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>150</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>40763428.2</v>
       </c>
       <c r="C5" t="n">
-        <v>123004728</v>
+        <v>93930883.2</v>
       </c>
       <c r="D5" t="n">
-        <v>107158619.95</v>
+        <v>203044064.26</v>
       </c>
       <c r="E5" t="n">
-        <v>11924757.13</v>
+        <v>22329793.8</v>
       </c>
       <c r="F5" t="n">
         <v>5833.38</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1192140.18</v>
+        <v>24562440</v>
       </c>
       <c r="I5" t="n">
-        <v>114999</v>
+        <v>128576.29</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1908539.64</v>
+        <v>3423343.67</v>
       </c>
       <c r="L5" t="n">
-        <v>412454.7</v>
+        <v>7886970</v>
+      </c>
+      <c r="M5" t="n">
+        <v>63180</v>
       </c>
     </row>
     <row r="6">
@@ -12712,34 +13659,37 @@
         <v>40729867.2</v>
       </c>
       <c r="C6" t="n">
-        <v>70403256</v>
+        <v>53762486.4</v>
       </c>
       <c r="D6" t="n">
-        <v>57411407.92</v>
+        <v>108783088.13</v>
       </c>
       <c r="E6" t="n">
-        <v>2886359.11</v>
+        <v>5404873.5</v>
       </c>
       <c r="F6" t="n">
         <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>38073</v>
+        <v>111375</v>
       </c>
       <c r="H6" t="n">
-        <v>217612.89</v>
+        <v>4483620</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>29166.5</v>
+        <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>1164836.4</v>
+        <v>2092520.82</v>
       </c>
       <c r="L6" t="n">
-        <v>282944.77</v>
+        <v>5408586</v>
+      </c>
+      <c r="M6" t="n">
+        <v>100800</v>
       </c>
     </row>
     <row r="7">
@@ -12750,34 +13700,37 @@
         <v>15886361.7</v>
       </c>
       <c r="C7" t="n">
-        <v>30547440</v>
+        <v>23327136</v>
       </c>
       <c r="D7" t="n">
-        <v>28212105.67</v>
+        <v>53456274.43</v>
       </c>
       <c r="E7" t="n">
-        <v>1022802.83</v>
+        <v>1915257.15</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>30386.25</v>
+        <v>88695</v>
       </c>
       <c r="H7" t="n">
-        <v>84820.89</v>
+        <v>1747620</v>
       </c>
       <c r="I7" t="n">
-        <v>210831.5</v>
+        <v>123914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>419853.12</v>
+        <v>743489.47</v>
       </c>
       <c r="L7" t="n">
-        <v>206015.4</v>
+        <v>3936600</v>
+      </c>
+      <c r="M7" t="n">
+        <v>248850</v>
       </c>
     </row>
     <row r="8">
@@ -12788,19 +13741,19 @@
         <v>3160278</v>
       </c>
       <c r="C8" t="n">
-        <v>6070680</v>
+        <v>4635792</v>
       </c>
       <c r="D8" t="n">
-        <v>6467778.79</v>
+        <v>12255141.89</v>
       </c>
       <c r="E8" t="n">
-        <v>122023.99</v>
+        <v>228496.95</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>17676.75</v>
+        <v>51597</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12812,10 +13765,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>153604.8</v>
+        <v>285897.73</v>
       </c>
       <c r="L8" t="n">
-        <v>72834.5</v>
+        <v>1391742</v>
+      </c>
+      <c r="M8" t="n">
+        <v>189000</v>
       </c>
     </row>
     <row r="9">
@@ -12826,19 +13782,19 @@
         <v>511236</v>
       </c>
       <c r="C9" t="n">
-        <v>942480</v>
+        <v>719712</v>
       </c>
       <c r="D9" t="n">
-        <v>1095538.62</v>
+        <v>2075825.66</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>8491.5</v>
+        <v>24786</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12850,10 +13806,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>21334</v>
+        <v>38990.47</v>
       </c>
       <c r="L9" t="n">
-        <v>30902.31</v>
+        <v>590490</v>
+      </c>
+      <c r="M9" t="n">
+        <v>144000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,22 +13823,22 @@
         <v>407484</v>
       </c>
       <c r="C10" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D10" t="n">
-        <v>209461.27</v>
+        <v>396887.04</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>90045</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>6660</v>
+        <v>19440</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -12891,7 +13850,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>25654.43</v>
+        <v>490212</v>
+      </c>
+      <c r="M10" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,10 +13864,10 @@
         <v>137610</v>
       </c>
       <c r="C11" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D11" t="n">
-        <v>180269.11</v>
+        <v>341573.76</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12914,7 +13876,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4995</v>
+        <v>14580</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12929,7 +13891,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>28542.6</v>
+        <v>545400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>135000</v>
       </c>
     </row>
     <row r="12">
@@ -12940,10 +13905,10 @@
         <v>50490</v>
       </c>
       <c r="C12" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D12" t="n">
-        <v>37197.43</v>
+        <v>70481.66</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12952,7 +13917,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>12151.8</v>
+        <v>232200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>29898</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12990,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13005,7 +13973,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1978.2</v>
+        <v>37800</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="14">
@@ -13016,10 +13987,10 @@
         <v>13464</v>
       </c>
       <c r="C14" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D14" t="n">
-        <v>117009.4</v>
+        <v>221709.31</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13028,7 +13999,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13040,10 +14011,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>21334</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>7347.6</v>
+        <v>140400</v>
+      </c>
+      <c r="M14" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>6336</v>
       </c>
       <c r="C15" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D15" t="n">
-        <v>276954.35</v>
+        <v>524772.86</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13066,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>68820</v>
+        <v>200880</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13081,7 +14055,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1413</v>
+        <v>27000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -13092,10 +14069,10 @@
         <v>594</v>
       </c>
       <c r="C16" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D16" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13104,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13119,6 +14096,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13159,6 +14139,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -13168,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13195,6 +14178,9 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13206,10 +14192,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D19" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13233,6 +14219,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13244,10 +14233,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D20" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13271,6 +14260,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13358,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13385,6 +14383,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D24" t="n">
-        <v>200633.4</v>
+        <v>380160</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13423,6 +14424,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>50160</v>
+        <v>50220</v>
       </c>
       <c r="H4" t="n">
         <v>3990</v>
@@ -13595,7 +14608,10 @@
         <v>61</v>
       </c>
       <c r="L4" t="n">
-        <v>177000</v>
+        <v>179070</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13633,7 +14649,10 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>47280</v>
+        <v>46860</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13656,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="H6" t="n">
         <v>210</v>
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8370</v>
+        <v>8790</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>540</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>90</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>90</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>180</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.3</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>9928.799999999999</v>
+        <v>9840.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14588,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>37.5</v>
+        <v>42</v>
       </c>
       <c r="H6" t="n">
         <v>119.7</v>
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3096.9</v>
+        <v>3252.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>324</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>63.9</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>160.2</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>3559455.9</v>
       </c>
       <c r="C5" t="n">
-        <v>10077606</v>
+        <v>7695626.4</v>
       </c>
       <c r="D5" t="n">
-        <v>8779356.439999999</v>
+        <v>16635117.31</v>
       </c>
       <c r="E5" t="n">
-        <v>3383558.39</v>
+        <v>6335907.75</v>
       </c>
       <c r="F5" t="n">
         <v>5000.04</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>104573.7</v>
+        <v>2154600</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>134404.2</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>93529.3</v>
+        <v>1771308</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,22 +16671,22 @@
         <v>534916.8</v>
       </c>
       <c r="C6" t="n">
-        <v>2320164</v>
+        <v>1771761.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1892013.09</v>
+        <v>3584984.83</v>
       </c>
       <c r="E6" t="n">
-        <v>476389.37</v>
+        <v>892066.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>693.75</v>
+        <v>2268</v>
       </c>
       <c r="H6" t="n">
-        <v>33115</v>
+        <v>682290</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>29172.8</v>
+        <v>585414</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,19 +16712,19 @@
         <v>166468.5</v>
       </c>
       <c r="C7" t="n">
-        <v>388080</v>
+        <v>296352</v>
       </c>
       <c r="D7" t="n">
-        <v>358411.51</v>
+        <v>679117.8199999999</v>
       </c>
       <c r="E7" t="n">
-        <v>70538.13</v>
+        <v>132086.7</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83.25</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3052.08</v>
+        <v>58320</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>2106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>601.9400000000001</v>
+        <v>11502</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>686.72</v>
+        <v>13122</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1509.08</v>
+        <v>28836</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15725,7 +16903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>110957121</v>
+        <v>110923530.3</v>
       </c>
       <c r="C5" t="n">
-        <v>434754936</v>
+        <v>331994678.4</v>
       </c>
       <c r="D5" t="n">
-        <v>378747546.68</v>
+        <v>717650537.47</v>
       </c>
       <c r="E5" t="n">
-        <v>56514569.83</v>
+        <v>105826783.5</v>
       </c>
       <c r="F5" t="n">
         <v>43333.68</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4030569.18</v>
+        <v>83044440</v>
       </c>
       <c r="I5" t="n">
-        <v>114999</v>
+        <v>128576.29</v>
       </c>
       <c r="J5" t="n">
-        <v>314998.2</v>
+        <v>131101.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5573294.16</v>
+        <v>9852158.07</v>
       </c>
       <c r="L5" t="n">
-        <v>1522699.67</v>
+        <v>29038338</v>
+      </c>
+      <c r="M5" t="n">
+        <v>183420</v>
       </c>
     </row>
     <row r="6">
@@ -16437,37 +17672,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>120710779.2</v>
+        <v>120707928</v>
       </c>
       <c r="C6" t="n">
-        <v>293039208</v>
+        <v>223775395.2</v>
       </c>
       <c r="D6" t="n">
-        <v>238963287.52</v>
+        <v>452787439.1</v>
       </c>
       <c r="E6" t="n">
-        <v>33403301.57</v>
+        <v>62549604</v>
       </c>
       <c r="F6" t="n">
         <v>133334.4</v>
       </c>
       <c r="G6" t="n">
-        <v>154290</v>
+        <v>448659</v>
       </c>
       <c r="H6" t="n">
-        <v>1078603.02</v>
+        <v>22223160</v>
       </c>
       <c r="I6" t="n">
-        <v>268331</v>
+        <v>196943.14</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>3674781.5</v>
+        <v>6499123.49</v>
       </c>
       <c r="L6" t="n">
-        <v>1210200.59</v>
+        <v>23072904</v>
+      </c>
+      <c r="M6" t="n">
+        <v>341280</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>77631315.3</v>
+        <v>77630374.8</v>
       </c>
       <c r="C7" t="n">
-        <v>155426040</v>
+        <v>118688976</v>
       </c>
       <c r="D7" t="n">
-        <v>143543808.06</v>
+        <v>271986688.51</v>
       </c>
       <c r="E7" t="n">
-        <v>22924891.08</v>
+        <v>42928177.5</v>
       </c>
       <c r="F7" t="n">
         <v>625005</v>
       </c>
       <c r="G7" t="n">
-        <v>195471</v>
+        <v>566919</v>
       </c>
       <c r="H7" t="n">
-        <v>218110.86</v>
+        <v>4493880</v>
       </c>
       <c r="I7" t="n">
-        <v>210831.5</v>
+        <v>123914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>204165.5</v>
+        <v>84973</v>
       </c>
       <c r="K7" t="n">
-        <v>2256710.52</v>
+        <v>3996255.91</v>
       </c>
       <c r="L7" t="n">
-        <v>1008203.76</v>
+        <v>19154880</v>
+      </c>
+      <c r="M7" t="n">
+        <v>948150</v>
       </c>
     </row>
     <row r="8">
@@ -16513,37 +17754,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>44465058</v>
+        <v>44464662</v>
       </c>
       <c r="C8" t="n">
-        <v>61372080</v>
+        <v>46865952</v>
       </c>
       <c r="D8" t="n">
-        <v>65386585.57</v>
+        <v>123894448.13</v>
       </c>
       <c r="E8" t="n">
-        <v>10494063.52</v>
+        <v>19650737.7</v>
       </c>
       <c r="F8" t="n">
         <v>237501.9</v>
       </c>
       <c r="G8" t="n">
-        <v>369408</v>
+        <v>1062477</v>
       </c>
       <c r="H8" t="n">
-        <v>42327.45</v>
+        <v>872100</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1497646.8</v>
+        <v>2787502.85</v>
       </c>
       <c r="L8" t="n">
-        <v>548566.16</v>
+        <v>10393974</v>
+      </c>
+      <c r="M8" t="n">
+        <v>847800</v>
       </c>
     </row>
     <row r="9">
@@ -16551,37 +17795,40 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>24579720</v>
+        <v>24579126</v>
       </c>
       <c r="C9" t="n">
-        <v>22425480</v>
+        <v>17124912</v>
       </c>
       <c r="D9" t="n">
-        <v>26067374.75</v>
+        <v>49392440.06</v>
       </c>
       <c r="E9" t="n">
-        <v>2752114.48</v>
+        <v>5153492.7</v>
       </c>
       <c r="F9" t="n">
         <v>83334</v>
       </c>
       <c r="G9" t="n">
-        <v>295315.5</v>
+        <v>846855</v>
       </c>
       <c r="H9" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>597352</v>
+        <v>1091733.1</v>
       </c>
       <c r="L9" t="n">
-        <v>225243.5</v>
+        <v>4251528</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1053000</v>
       </c>
     </row>
     <row r="10">
@@ -16592,22 +17839,22 @@
         <v>12255210</v>
       </c>
       <c r="C10" t="n">
-        <v>5072760</v>
+        <v>3873744</v>
       </c>
       <c r="D10" t="n">
-        <v>6388568.72</v>
+        <v>12105054.72</v>
       </c>
       <c r="E10" t="n">
-        <v>528953.04</v>
+        <v>990495</v>
       </c>
       <c r="F10" t="n">
         <v>41667</v>
       </c>
       <c r="G10" t="n">
-        <v>140970</v>
+        <v>411480</v>
       </c>
       <c r="H10" t="n">
-        <v>41497.5</v>
+        <v>855000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16616,10 +17863,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>149338</v>
+        <v>295706.04</v>
       </c>
       <c r="L10" t="n">
-        <v>119469.15</v>
+        <v>2268432</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1242000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,19 +17880,19 @@
         <v>5010588</v>
       </c>
       <c r="C11" t="n">
-        <v>1995840</v>
+        <v>1524096</v>
       </c>
       <c r="D11" t="n">
-        <v>2595875.18</v>
+        <v>4918662.14</v>
       </c>
       <c r="E11" t="n">
-        <v>203854.19</v>
+        <v>381728.7</v>
       </c>
       <c r="F11" t="n">
         <v>125001</v>
       </c>
       <c r="G11" t="n">
-        <v>29970</v>
+        <v>87480</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -16657,7 +17907,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>59628.6</v>
+        <v>1085400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>306000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,19 +17921,19 @@
         <v>2771802</v>
       </c>
       <c r="C12" t="n">
-        <v>1025640</v>
+        <v>783216</v>
       </c>
       <c r="D12" t="n">
-        <v>1376305</v>
+        <v>2607821.57</v>
       </c>
       <c r="E12" t="n">
-        <v>237780.14</v>
+        <v>445257</v>
       </c>
       <c r="F12" t="n">
         <v>41667</v>
       </c>
       <c r="G12" t="n">
-        <v>23865</v>
+        <v>69660</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -16695,7 +17948,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>28825.2</v>
+        <v>518400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="13">
@@ -16706,10 +17962,10 @@
         <v>2354022</v>
       </c>
       <c r="C13" t="n">
-        <v>526680</v>
+        <v>402192</v>
       </c>
       <c r="D13" t="n">
-        <v>723905.37</v>
+        <v>1371655.3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16718,10 +17974,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>9990</v>
+        <v>29160</v>
       </c>
       <c r="H13" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -16730,10 +17986,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21334</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>6499.8</v>
+        <v>124200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="14">
@@ -16744,10 +18003,10 @@
         <v>2229678</v>
       </c>
       <c r="C14" t="n">
-        <v>332640</v>
+        <v>254016</v>
       </c>
       <c r="D14" t="n">
-        <v>468037.6</v>
+        <v>886837.25</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16756,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>12210</v>
+        <v>35640</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -16768,10 +18027,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>21334</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>13847.4</v>
+        <v>264600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>252000</v>
       </c>
     </row>
     <row r="15">
@@ -16782,10 +18044,10 @@
         <v>1062468</v>
       </c>
       <c r="C15" t="n">
-        <v>360360</v>
+        <v>275184</v>
       </c>
       <c r="D15" t="n">
-        <v>514343.78</v>
+        <v>974578.1800000001</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16794,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>69930</v>
+        <v>204120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -16809,7 +18071,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1978.2</v>
+        <v>37800</v>
+      </c>
+      <c r="M15" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="16">
@@ -16820,10 +18085,10 @@
         <v>435600</v>
       </c>
       <c r="C16" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D16" t="n">
-        <v>200633.4</v>
+        <v>380160</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16832,7 +18097,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -16847,7 +18112,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="17">
@@ -16887,6 +18155,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -16896,10 +18167,10 @@
         <v>8118</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16924,6 +18195,9 @@
       </c>
       <c r="L18" t="n">
         <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="19">
@@ -16934,10 +18208,10 @@
         <v>14256</v>
       </c>
       <c r="C19" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D19" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16962,6 +18236,9 @@
       </c>
       <c r="L19" t="n">
         <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="20">
@@ -16972,10 +18249,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D20" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16999,6 +18276,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17039,6 +18319,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17048,10 +18331,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17075,6 +18358,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17086,10 +18372,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17113,6 +18399,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17124,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D24" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17151,6 +18440,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>31848.93</v>
+        <v>31768.83</v>
       </c>
       <c r="C4" t="n">
         <v>5103504</v>
@@ -17308,7 +18609,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>105120</v>
+        <v>102600</v>
       </c>
       <c r="H4" t="n">
         <v>6090</v>
@@ -17320,10 +18621,13 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="L4" t="n">
-        <v>261000</v>
+        <v>258270</v>
+      </c>
+      <c r="M4" t="n">
+        <v>24270</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>34106.76</v>
+        <v>34082.91</v>
       </c>
       <c r="C5" t="n">
         <v>3958416</v>
@@ -17346,7 +18650,7 @@
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>82440</v>
+        <v>81630</v>
       </c>
       <c r="H5" t="n">
         <v>1440</v>
@@ -17358,10 +18662,13 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="L5" t="n">
-        <v>215790</v>
+        <v>214410</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6090</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>27134.55</v>
+        <v>27132.93</v>
       </c>
       <c r="C6" t="n">
         <v>2691360</v>
@@ -17384,7 +18691,7 @@
         <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>75000</v>
+        <v>74340</v>
       </c>
       <c r="H6" t="n">
         <v>30</v>
@@ -17396,10 +18703,13 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L6" t="n">
-        <v>142080</v>
+        <v>141300</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4200</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>18697.95</v>
+        <v>18697.5</v>
       </c>
       <c r="C7" t="n">
         <v>1588104</v>
@@ -17422,7 +18732,7 @@
         <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>42120</v>
+        <v>41730</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -17437,7 +18747,10 @@
         <v>92</v>
       </c>
       <c r="L7" t="n">
-        <v>94320</v>
+        <v>93300</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3030</v>
       </c>
     </row>
     <row r="8">
@@ -17445,7 +18758,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>12020.76</v>
+        <v>12020.67</v>
       </c>
       <c r="C8" t="n">
         <v>784224</v>
@@ -17460,7 +18773,7 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>17340</v>
+        <v>16890</v>
       </c>
       <c r="H8" t="n">
         <v>30</v>
@@ -17475,7 +18788,10 @@
         <v>65</v>
       </c>
       <c r="L8" t="n">
-        <v>52290</v>
+        <v>51600</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1920</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>15660</v>
+        <v>15330</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -17513,7 +18829,10 @@
         <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>20280</v>
+        <v>19920</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2550</v>
       </c>
     </row>
     <row r="10">
@@ -17551,7 +18870,10 @@
         <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>5730</v>
+        <v>5640</v>
+      </c>
+      <c r="M10" t="n">
+        <v>780</v>
       </c>
     </row>
     <row r="11">
@@ -17589,7 +18911,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2070</v>
+        <v>1770</v>
+      </c>
+      <c r="M11" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="12">
@@ -17627,7 +18952,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>870</v>
+        <v>690</v>
+      </c>
+      <c r="M12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>210</v>
       </c>
+      <c r="M13" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>150</v>
       </c>
+      <c r="M14" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>60</v>
       </c>
+      <c r="M15" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>60</v>
       </c>
+      <c r="M16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>15348.04</v>
+        <v>15337.31</v>
       </c>
       <c r="C5" t="n">
         <v>2177128.8</v>
@@ -18290,10 +19666,13 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>92.81999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="L5" t="n">
-        <v>45315.9</v>
+        <v>45026.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>121.8</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>21707.64</v>
+        <v>21706.34</v>
       </c>
       <c r="C6" t="n">
         <v>2422224</v>
@@ -18316,7 +19695,7 @@
         <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>3750</v>
+        <v>3717</v>
       </c>
       <c r="H6" t="n">
         <v>17.1</v>
@@ -18328,10 +19707,13 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>89.7</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>52569.6</v>
+        <v>52281</v>
+      </c>
+      <c r="M6" t="n">
+        <v>336</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>17763.05</v>
+        <v>17762.62</v>
       </c>
       <c r="C7" t="n">
         <v>1588104</v>
@@ -18354,7 +19736,7 @@
         <v>12.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6318</v>
+        <v>6259.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -18366,10 +19748,13 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>75.44</v>
+        <v>58.7</v>
       </c>
       <c r="L7" t="n">
-        <v>56592</v>
+        <v>55980</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1060.5</v>
       </c>
     </row>
     <row r="8">
@@ -18377,7 +19762,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>12020.76</v>
+        <v>12020.67</v>
       </c>
       <c r="C8" t="n">
         <v>784224</v>
@@ -18392,7 +19777,7 @@
         <v>2.85</v>
       </c>
       <c r="G8" t="n">
-        <v>11271</v>
+        <v>10978.5</v>
       </c>
       <c r="H8" t="n">
         <v>25.5</v>
@@ -18404,10 +19789,13 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>58.5</v>
+        <v>47.84</v>
       </c>
       <c r="L8" t="n">
-        <v>37125.9</v>
+        <v>36636</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1152</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>13311</v>
+        <v>13030.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -18442,10 +19830,13 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>19.27</v>
       </c>
       <c r="L9" t="n">
-        <v>16426.8</v>
+        <v>16135.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2550</v>
       </c>
     </row>
     <row r="10">
@@ -18480,10 +19871,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>5.22</v>
       </c>
       <c r="L10" t="n">
-        <v>5099.7</v>
+        <v>5019.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>780</v>
       </c>
     </row>
     <row r="11">
@@ -18521,7 +19915,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2070</v>
+        <v>1770</v>
+      </c>
+      <c r="M11" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="12">
@@ -18559,7 +19956,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>870</v>
+        <v>690</v>
+      </c>
+      <c r="M12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -18594,10 +19994,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>210</v>
+      </c>
+      <c r="M13" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -18637,6 +20040,9 @@
       <c r="L14" t="n">
         <v>150</v>
       </c>
+      <c r="M14" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18675,6 +20081,9 @@
       <c r="L15" t="n">
         <v>60</v>
       </c>
+      <c r="M15" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>60</v>
       </c>
+      <c r="M16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>33765692.4</v>
+        <v>33742080.9</v>
       </c>
       <c r="C5" t="n">
-        <v>119742084</v>
+        <v>91439409.59999999</v>
       </c>
       <c r="D5" t="n">
-        <v>104316286.7</v>
+        <v>197658413.57</v>
       </c>
       <c r="E5" t="n">
-        <v>22112011.3</v>
+        <v>41406013.35</v>
       </c>
       <c r="F5" t="n">
         <v>6666.72</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>143415.36</v>
+        <v>2954880</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K5" t="n">
-        <v>1980221.88</v>
+        <v>3423343.67</v>
       </c>
       <c r="L5" t="n">
-        <v>426875.78</v>
+        <v>8104698</v>
+      </c>
+      <c r="M5" t="n">
+        <v>36540</v>
       </c>
     </row>
     <row r="6">
@@ -19233,37 +20684,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>47756808</v>
+        <v>47753956.8</v>
       </c>
       <c r="C6" t="n">
-        <v>133222320</v>
+        <v>101733408</v>
       </c>
       <c r="D6" t="n">
-        <v>108638170.9</v>
+        <v>205847516.16</v>
       </c>
       <c r="E6" t="n">
-        <v>20148467.98</v>
+        <v>37729165.5</v>
       </c>
       <c r="F6" t="n">
         <v>58333.8</v>
       </c>
       <c r="G6" t="n">
-        <v>69375</v>
+        <v>200718</v>
       </c>
       <c r="H6" t="n">
-        <v>4730.71</v>
+        <v>97470</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>1913659.8</v>
+        <v>3372651.2</v>
       </c>
       <c r="L6" t="n">
-        <v>495205.63</v>
+        <v>9410580</v>
+      </c>
+      <c r="M6" t="n">
+        <v>100800</v>
       </c>
     </row>
     <row r="7">
@@ -19271,22 +20725,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>39078715.5</v>
+        <v>39077775</v>
       </c>
       <c r="C7" t="n">
-        <v>87345720</v>
+        <v>66700368</v>
       </c>
       <c r="D7" t="n">
-        <v>80668189.62</v>
+        <v>152850018.82</v>
       </c>
       <c r="E7" t="n">
-        <v>17493455.35</v>
+        <v>32757501.6</v>
       </c>
       <c r="F7" t="n">
         <v>525004.2</v>
       </c>
       <c r="G7" t="n">
-        <v>116883</v>
+        <v>338013</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -19295,13 +20749,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1609436.96</v>
+        <v>2850042.98</v>
       </c>
       <c r="L7" t="n">
-        <v>533096.64</v>
+        <v>10076400</v>
+      </c>
+      <c r="M7" t="n">
+        <v>318150</v>
       </c>
     </row>
     <row r="8">
@@ -19309,37 +20766,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>26445672</v>
+        <v>26445474</v>
       </c>
       <c r="C8" t="n">
-        <v>43132320</v>
+        <v>32937408</v>
       </c>
       <c r="D8" t="n">
-        <v>45953715.96</v>
+        <v>87073062.91</v>
       </c>
       <c r="E8" t="n">
-        <v>9355172.9</v>
+        <v>17518099.5</v>
       </c>
       <c r="F8" t="n">
         <v>118750.95</v>
       </c>
       <c r="G8" t="n">
-        <v>208513.5</v>
+        <v>592839</v>
       </c>
       <c r="H8" t="n">
-        <v>7054.58</v>
+        <v>145350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1248039</v>
+        <v>2322919.04</v>
       </c>
       <c r="L8" t="n">
-        <v>349725.98</v>
+        <v>6594480</v>
+      </c>
+      <c r="M8" t="n">
+        <v>345600</v>
       </c>
     </row>
     <row r="9">
@@ -19350,19 +20810,19 @@
         <v>16438158</v>
       </c>
       <c r="C9" t="n">
-        <v>17435880</v>
+        <v>13314672</v>
       </c>
       <c r="D9" t="n">
-        <v>20267464.42</v>
+        <v>38402774.78</v>
       </c>
       <c r="E9" t="n">
-        <v>2219447.16</v>
+        <v>4156042.5</v>
       </c>
       <c r="F9" t="n">
         <v>41667</v>
       </c>
       <c r="G9" t="n">
-        <v>246253.5</v>
+        <v>703647</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -19371,13 +20831,16 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>512016</v>
+        <v>935771.23</v>
       </c>
       <c r="L9" t="n">
-        <v>154740.46</v>
+        <v>2904336</v>
+      </c>
+      <c r="M9" t="n">
+        <v>765000</v>
       </c>
     </row>
     <row r="10">
@@ -19388,19 +20851,19 @@
         <v>7901982</v>
       </c>
       <c r="C10" t="n">
-        <v>2993760</v>
+        <v>2286144</v>
       </c>
       <c r="D10" t="n">
-        <v>3770302.85</v>
+        <v>7143966.72</v>
       </c>
       <c r="E10" t="n">
-        <v>336606.48</v>
+        <v>630315</v>
       </c>
       <c r="F10" t="n">
         <v>41667</v>
       </c>
       <c r="G10" t="n">
-        <v>117660</v>
+        <v>343440</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -19412,10 +20875,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>128004</v>
+        <v>253462.32</v>
       </c>
       <c r="L10" t="n">
-        <v>48039.17</v>
+        <v>903528</v>
+      </c>
+      <c r="M10" t="n">
+        <v>234000</v>
       </c>
     </row>
     <row r="11">
@@ -19426,19 +20892,19 @@
         <v>2575584</v>
       </c>
       <c r="C11" t="n">
-        <v>970200</v>
+        <v>740880</v>
       </c>
       <c r="D11" t="n">
-        <v>1261883.77</v>
+        <v>2391016.32</v>
       </c>
       <c r="E11" t="n">
-        <v>135902.79</v>
+        <v>254485.8</v>
       </c>
       <c r="F11" t="n">
         <v>83334</v>
       </c>
       <c r="G11" t="n">
-        <v>18870</v>
+        <v>55080</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -19453,7 +20919,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>19499.4</v>
+        <v>318600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>153000</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>925848</v>
       </c>
       <c r="C12" t="n">
-        <v>637560</v>
+        <v>486864</v>
       </c>
       <c r="D12" t="n">
-        <v>855540.9399999999</v>
+        <v>1621078.27</v>
       </c>
       <c r="E12" t="n">
-        <v>237780.14</v>
+        <v>445257</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>15540</v>
+        <v>45360</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19491,7 +20960,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>8195.4</v>
+        <v>124200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="13">
@@ -19502,10 +20974,10 @@
         <v>502524</v>
       </c>
       <c r="C13" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D13" t="n">
-        <v>266701.98</v>
+        <v>505346.69</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -19514,7 +20986,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>5550</v>
+        <v>16200</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19526,10 +20998,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21334</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>1978.2</v>
+        <v>37800</v>
+      </c>
+      <c r="M13" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="14">
@@ -19540,10 +21015,10 @@
         <v>336402</v>
       </c>
       <c r="C14" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D14" t="n">
-        <v>78006.27</v>
+        <v>147806.21</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -19552,7 +21027,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -19567,7 +21042,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1413</v>
+        <v>27000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>162000</v>
       </c>
     </row>
     <row r="15">
@@ -19578,10 +21056,10 @@
         <v>242946</v>
       </c>
       <c r="C15" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D15" t="n">
-        <v>39564.91</v>
+        <v>74967.55</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -19590,7 +21068,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -19605,7 +21083,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M15" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="16">
@@ -19628,7 +21109,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -19643,7 +21124,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="17">
@@ -19683,6 +21167,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -19721,6 +21208,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>9000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -19730,10 +21220,10 @@
         <v>13860</v>
       </c>
       <c r="C19" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D19" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19758,6 +21248,9 @@
       </c>
       <c r="L19" t="n">
         <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="20">
@@ -19797,6 +21290,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19835,6 +21331,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19873,6 +21372,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19920,10 +21425,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D24" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19947,6 +21452,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,7 +21621,7 @@
         <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>110520</v>
+        <v>110730</v>
       </c>
       <c r="H4" t="n">
         <v>28470</v>
@@ -20119,7 +21636,10 @@
         <v>216</v>
       </c>
       <c r="L4" t="n">
-        <v>311070</v>
+        <v>310110</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,10 +21662,10 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>53910</v>
+        <v>54030</v>
       </c>
       <c r="H5" t="n">
-        <v>18660</v>
+        <v>18690</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20157,7 +21677,10 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>116400</v>
+        <v>117150</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20180,10 +21703,10 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>10920</v>
+        <v>11010</v>
       </c>
       <c r="H6" t="n">
-        <v>1170</v>
+        <v>1200</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20195,7 +21718,10 @@
         <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>26160</v>
+        <v>25950</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20233,7 +21759,10 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>5160</v>
+        <v>5130</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -20256,7 +21785,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H8" t="n">
         <v>60</v>
@@ -20272,6 +21801,9 @@
       </c>
       <c r="L8" t="n">
         <v>750</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -20311,6 +21843,9 @@
       <c r="L9" t="n">
         <v>450</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>30</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21077,7 +22669,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6717.6</v>
+        <v>6728.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21086,10 +22678,13 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>42</v>
+        <v>33.1</v>
       </c>
       <c r="L5" t="n">
-        <v>24444</v>
+        <v>24601.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21112,10 +22707,10 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>546</v>
+        <v>550.5</v>
       </c>
       <c r="H6" t="n">
-        <v>666.9</v>
+        <v>684</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.85</v>
+        <v>4.56</v>
       </c>
       <c r="L6" t="n">
-        <v>9679.200000000001</v>
+        <v>9601.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21162,10 +22760,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>3096</v>
+        <v>3078</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21188,7 +22789,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>58.5</v>
+        <v>78</v>
       </c>
       <c r="H8" t="n">
         <v>51</v>
@@ -21204,6 +22805,9 @@
       </c>
       <c r="L8" t="n">
         <v>532.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21243,6 +22847,9 @@
       <c r="L9" t="n">
         <v>364.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>26.7</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>12378573.9</v>
       </c>
       <c r="C5" t="n">
-        <v>44579304</v>
+        <v>34042377.6</v>
       </c>
       <c r="D5" t="n">
-        <v>38836366.48</v>
+        <v>73587115.01000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3438426.9</v>
+        <v>6438652.2</v>
       </c>
       <c r="F5" t="n">
         <v>4166.7</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1858424.04</v>
+        <v>38351880</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>104999.4</v>
+        <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>896028</v>
+        <v>1607203.6</v>
       </c>
       <c r="L5" t="n">
-        <v>230262.48</v>
+        <v>4428270</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,22 +23699,22 @@
         <v>3627676.8</v>
       </c>
       <c r="C6" t="n">
-        <v>13097700</v>
+        <v>10001880</v>
       </c>
       <c r="D6" t="n">
-        <v>10680719.05</v>
+        <v>20237817.6</v>
       </c>
       <c r="E6" t="n">
-        <v>700572.6</v>
+        <v>1311862.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>10101</v>
+        <v>29727</v>
       </c>
       <c r="H6" t="n">
-        <v>184497.88</v>
+        <v>3898800</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -22056,10 +23723,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>124803.9</v>
+        <v>221561.03</v>
       </c>
       <c r="L6" t="n">
-        <v>91178.06</v>
+        <v>1728270</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,22 +23740,22 @@
         <v>400653</v>
       </c>
       <c r="C7" t="n">
-        <v>1857240</v>
+        <v>1418256</v>
       </c>
       <c r="D7" t="n">
-        <v>1715255.06</v>
+        <v>3250063.87</v>
       </c>
       <c r="E7" t="n">
-        <v>211614.38</v>
+        <v>396260.1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1748.25</v>
+        <v>5103</v>
       </c>
       <c r="H7" t="n">
-        <v>84820.89</v>
+        <v>1747620</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22094,10 +23764,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>17493.88</v>
+        <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>29164.32</v>
+        <v>554040</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,10 +23781,10 @@
         <v>79002</v>
       </c>
       <c r="C8" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D8" t="n">
-        <v>236265.89</v>
+        <v>447676.42</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -22120,10 +23793,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1082.25</v>
+        <v>4212</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22135,7 +23808,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5016.15</v>
+        <v>95850</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22146,10 +23822,10 @@
         <v>33858</v>
       </c>
       <c r="C9" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D9" t="n">
-        <v>64443.45</v>
+        <v>122107.39</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22161,7 +23837,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3433.59</v>
+        <v>65610</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22199,7 +23878,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>251.51</v>
+        <v>4806</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22251,6 +23933,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -22289,6 +23974,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
@@ -549,7 +549,7 @@
         <v>33</v>
       </c>
       <c r="K4" t="n">
-        <v>907</v>
+        <v>334</v>
       </c>
       <c r="L4" t="n">
         <v>1288470</v>
@@ -590,7 +590,7 @@
         <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>613</v>
+        <v>171</v>
       </c>
       <c r="L5" t="n">
         <v>768210</v>
@@ -631,7 +631,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>264</v>
+        <v>64</v>
       </c>
       <c r="L6" t="n">
         <v>346440</v>
@@ -672,7 +672,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
         <v>177360</v>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
         <v>81330</v>
@@ -754,7 +754,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>29160</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>14160</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>690</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1470</v>
@@ -1553,7 +1553,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>104790</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
         <v>93420</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>45180</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>19620</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>8580</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2160</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>4260</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>17.21</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>19618.2</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>14.7</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>16716.6</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>11772</v>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>6091.8</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1749.6</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>3791.4</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>835745.87</v>
+        <v>208936.47</v>
       </c>
       <c r="L5" t="n">
         <v>3531276</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>713918.87</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
         <v>3008988</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>309787.28</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2118960</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>142948.86</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1096524</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>77980.94</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>314928</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>42243.72</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>682452</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="L4" t="n">
         <v>86220</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>25230</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3.97</v>
+        <v>1.99</v>
       </c>
       <c r="L5" t="n">
         <v>5298.3</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>192864.43</v>
+        <v>96432.22</v>
       </c>
       <c r="L5" t="n">
         <v>953694</v>
@@ -7577,7 +7577,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>27300</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>8190</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1380</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>30</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>1719.9</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>510.6</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>80360.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>309582</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>49235.78</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>91908</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>61957.46</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3240</v>
@@ -10589,7 +10589,7 @@
         <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="L4" t="n">
         <v>264330</v>
@@ -10630,7 +10630,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>213</v>
+        <v>65</v>
       </c>
       <c r="L5" t="n">
         <v>208650</v>
@@ -10671,7 +10671,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
         <v>81210</v>
@@ -10712,7 +10712,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>36450</v>
@@ -10753,7 +10753,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>10890</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>4050</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>780</v>
@@ -11634,7 +11634,7 @@
         <v>5.4</v>
       </c>
       <c r="K5" t="n">
-        <v>202.9</v>
+        <v>56.6</v>
       </c>
       <c r="L5" t="n">
         <v>161324.1</v>
@@ -11675,7 +11675,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>133.85</v>
+        <v>32.45</v>
       </c>
       <c r="L6" t="n">
         <v>128182.8</v>
@@ -11716,7 +11716,7 @@
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>82.3</v>
+        <v>19.14</v>
       </c>
       <c r="L7" t="n">
         <v>106416</v>
@@ -11757,7 +11757,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>57.41</v>
+        <v>8.1</v>
       </c>
       <c r="L8" t="n">
         <v>57744.3</v>
@@ -11798,7 +11798,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>22.48</v>
+        <v>2.41</v>
       </c>
       <c r="L9" t="n">
         <v>23619.6</v>
@@ -11839,7 +11839,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>12602.4</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>690</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1470</v>
@@ -12638,7 +12638,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>70.5</v>
+        <v>21.52</v>
       </c>
       <c r="L5" t="n">
         <v>43816.5</v>
@@ -12679,7 +12679,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>43.1</v>
+        <v>12.17</v>
       </c>
       <c r="L6" t="n">
         <v>30047.7</v>
@@ -12720,7 +12720,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>15.31</v>
+        <v>2.55</v>
       </c>
       <c r="L7" t="n">
         <v>21870</v>
@@ -12761,7 +12761,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>5.89</v>
+        <v>2.94</v>
       </c>
       <c r="L8" t="n">
         <v>7731.9</v>
@@ -12802,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>3280.5</v>
@@ -13007,7 +13007,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>780</v>
@@ -13642,7 +13642,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3423343.67</v>
+        <v>1044682.34</v>
       </c>
       <c r="L5" t="n">
         <v>7886970</v>
@@ -13683,7 +13683,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>2092520.82</v>
+        <v>590829.41</v>
       </c>
       <c r="L6" t="n">
         <v>5408586</v>
@@ -13724,7 +13724,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>743489.47</v>
+        <v>123914.91</v>
       </c>
       <c r="L7" t="n">
         <v>3936600</v>
@@ -13765,7 +13765,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>285897.73</v>
+        <v>142948.86</v>
       </c>
       <c r="L8" t="n">
         <v>1391742</v>
@@ -13806,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>38990.47</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>590490</v>
@@ -14011,7 +14011,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>47196.43</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>140400</v>
@@ -14605,7 +14605,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
         <v>179070</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>46860</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.96</v>
+        <v>3.31</v>
       </c>
       <c r="L5" t="n">
         <v>9840.6</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>241080.54</v>
+        <v>160720.36</v>
       </c>
       <c r="L5" t="n">
         <v>1771308</v>
@@ -17658,7 +17658,7 @@
         <v>131101.2</v>
       </c>
       <c r="K5" t="n">
-        <v>9852158.07</v>
+        <v>2748318.16</v>
       </c>
       <c r="L5" t="n">
         <v>29038338</v>
@@ -17699,7 +17699,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>6499123.49</v>
+        <v>1575545.09</v>
       </c>
       <c r="L6" t="n">
         <v>23072904</v>
@@ -17740,7 +17740,7 @@
         <v>84973</v>
       </c>
       <c r="K7" t="n">
-        <v>3996255.91</v>
+        <v>929361.84</v>
       </c>
       <c r="L7" t="n">
         <v>19154880</v>
@@ -17781,7 +17781,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2787502.85</v>
+        <v>393109.38</v>
       </c>
       <c r="L8" t="n">
         <v>10393974</v>
@@ -17822,7 +17822,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1091733.1</v>
+        <v>116971.4</v>
       </c>
       <c r="L9" t="n">
         <v>4251528</v>
@@ -17863,7 +17863,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>295706.04</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2268432</v>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>46103.92</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>124200</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>47196.43</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>264600</v>
@@ -18621,7 +18621,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>253</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
         <v>258270</v>
@@ -18662,7 +18662,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>213</v>
+        <v>59</v>
       </c>
       <c r="L5" t="n">
         <v>214410</v>
@@ -18703,7 +18703,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
         <v>141300</v>
@@ -18744,7 +18744,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
         <v>93300</v>
@@ -18785,7 +18785,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
         <v>51600</v>
@@ -18826,7 +18826,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>19920</v>
@@ -18867,7 +18867,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>5640</v>
@@ -18990,7 +18990,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>210</v>
@@ -19666,7 +19666,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>70.5</v>
+        <v>19.53</v>
       </c>
       <c r="L5" t="n">
         <v>45026.1</v>
@@ -19707,7 +19707,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>69.45999999999999</v>
+        <v>18.25</v>
       </c>
       <c r="L6" t="n">
         <v>52281</v>
@@ -19748,7 +19748,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>58.7</v>
+        <v>16.59</v>
       </c>
       <c r="L7" t="n">
         <v>55980</v>
@@ -19789,7 +19789,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>47.84</v>
+        <v>5.15</v>
       </c>
       <c r="L8" t="n">
         <v>36636</v>
@@ -19830,7 +19830,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>19.27</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>16135.2</v>
@@ -19871,7 +19871,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>5019.6</v>
@@ -19994,7 +19994,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>210</v>
@@ -20670,7 +20670,7 @@
         <v>36417</v>
       </c>
       <c r="K5" t="n">
-        <v>3423343.67</v>
+        <v>948250.12</v>
       </c>
       <c r="L5" t="n">
         <v>8104698</v>
@@ -20711,7 +20711,7 @@
         <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>3372651.2</v>
+        <v>886244.11</v>
       </c>
       <c r="L6" t="n">
         <v>9410580</v>
@@ -20752,7 +20752,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2850042.98</v>
+        <v>805446.9300000001</v>
       </c>
       <c r="L7" t="n">
         <v>10076400</v>
@@ -20793,7 +20793,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2322919.04</v>
+        <v>250160.51</v>
       </c>
       <c r="L8" t="n">
         <v>6594480</v>
@@ -20834,7 +20834,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>935771.23</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
         <v>2904336</v>
@@ -20875,7 +20875,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>253462.32</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>903528</v>
@@ -20998,7 +20998,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>46103.92</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>37800</v>
@@ -21633,7 +21633,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>216</v>
+        <v>66</v>
       </c>
       <c r="L4" t="n">
         <v>310110</v>
@@ -21674,7 +21674,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
         <v>117150</v>
@@ -21715,7 +21715,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>25950</v>
@@ -21756,7 +21756,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>5130</v>
@@ -22678,7 +22678,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>33.1</v>
+        <v>5.96</v>
       </c>
       <c r="L5" t="n">
         <v>24601.5</v>
@@ -22719,7 +22719,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.56</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>9601.5</v>
@@ -22760,7 +22760,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3078</v>
@@ -23682,7 +23682,7 @@
         <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>1607203.6</v>
+        <v>289296.65</v>
       </c>
       <c r="L5" t="n">
         <v>4428270</v>
@@ -23723,7 +23723,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>221561.03</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>1728270</v>
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>30978.73</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>554040</v>

--- a/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Breaches.xlsx
@@ -560,7 +560,7 @@
         <v>477180</v>
       </c>
       <c r="H4" t="n">
-        <v>63450</v>
+        <v>70800</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -572,22 +572,22 @@
         <v>334</v>
       </c>
       <c r="L4" t="n">
-        <v>1288470</v>
+        <v>1423290</v>
       </c>
       <c r="M4" t="n">
-        <v>59940</v>
+        <v>60570</v>
       </c>
       <c r="N4" t="n">
-        <v>48420</v>
+        <v>61860</v>
       </c>
       <c r="O4" t="n">
-        <v>244320</v>
+        <v>263160</v>
       </c>
       <c r="P4" t="n">
-        <v>69090</v>
+        <v>26760</v>
       </c>
       <c r="Q4" t="n">
-        <v>190590.93</v>
+        <v>1975075.33</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>315360</v>
       </c>
       <c r="H5" t="n">
-        <v>40470</v>
+        <v>46650</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -625,22 +625,22 @@
         <v>171</v>
       </c>
       <c r="L5" t="n">
-        <v>768210</v>
+        <v>861510</v>
       </c>
       <c r="M5" t="n">
-        <v>30570</v>
+        <v>50250</v>
       </c>
       <c r="N5" t="n">
-        <v>14280</v>
+        <v>18900</v>
       </c>
       <c r="O5" t="n">
-        <v>178080</v>
+        <v>203730</v>
       </c>
       <c r="P5" t="n">
-        <v>77430</v>
+        <v>58500</v>
       </c>
       <c r="Q5" t="n">
-        <v>138934.52</v>
+        <v>1439765.01</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>166170</v>
       </c>
       <c r="H6" t="n">
-        <v>6840</v>
+        <v>9030</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -678,22 +678,22 @@
         <v>64</v>
       </c>
       <c r="L6" t="n">
-        <v>346440</v>
+        <v>397200</v>
       </c>
       <c r="M6" t="n">
-        <v>14220</v>
+        <v>36060</v>
       </c>
       <c r="N6" t="n">
-        <v>3990</v>
+        <v>8370</v>
       </c>
       <c r="O6" t="n">
-        <v>85860</v>
+        <v>105990</v>
       </c>
       <c r="P6" t="n">
-        <v>79740</v>
+        <v>60810</v>
       </c>
       <c r="Q6" t="n">
-        <v>85044.22</v>
+        <v>881305.04</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>69990</v>
       </c>
       <c r="H7" t="n">
-        <v>1080</v>
+        <v>1620</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -731,22 +731,22 @@
         <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>177360</v>
+        <v>216330</v>
       </c>
       <c r="M7" t="n">
-        <v>9030</v>
+        <v>30090</v>
       </c>
       <c r="N7" t="n">
-        <v>270</v>
+        <v>1470</v>
       </c>
       <c r="O7" t="n">
-        <v>29610</v>
+        <v>53400</v>
       </c>
       <c r="P7" t="n">
-        <v>87480</v>
+        <v>84720</v>
       </c>
       <c r="Q7" t="n">
-        <v>46058.21</v>
+        <v>477296.8</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>30270</v>
       </c>
       <c r="H8" t="n">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -784,22 +784,22 @@
         <v>11</v>
       </c>
       <c r="L8" t="n">
-        <v>81330</v>
+        <v>119130</v>
       </c>
       <c r="M8" t="n">
-        <v>4710</v>
+        <v>27300</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O8" t="n">
-        <v>7590</v>
+        <v>21330</v>
       </c>
       <c r="P8" t="n">
-        <v>81120</v>
+        <v>90480</v>
       </c>
       <c r="Q8" t="n">
-        <v>25061.9</v>
+        <v>259714.05</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>18450</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>29160</v>
+        <v>64650</v>
       </c>
       <c r="M9" t="n">
-        <v>3510</v>
+        <v>29040</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>720</v>
+        <v>4170</v>
       </c>
       <c r="P9" t="n">
-        <v>80790</v>
+        <v>119070</v>
       </c>
       <c r="Q9" t="n">
-        <v>13853.69</v>
+        <v>143564.44</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>7620</v>
       </c>
       <c r="H10" t="n">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,22 +890,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>14160</v>
+        <v>45660</v>
       </c>
       <c r="M10" t="n">
-        <v>4140</v>
+        <v>18660</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="P10" t="n">
-        <v>60360</v>
+        <v>104130</v>
       </c>
       <c r="Q10" t="n">
-        <v>6907.48</v>
+        <v>71581.57000000001</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>1620</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6030</v>
+        <v>32790</v>
       </c>
       <c r="M11" t="n">
-        <v>1020</v>
+        <v>6600</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
-        <v>38220</v>
+        <v>65550</v>
       </c>
       <c r="Q11" t="n">
-        <v>2824.15</v>
+        <v>29266.39</v>
       </c>
     </row>
     <row r="12">
@@ -996,22 +996,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2880</v>
+        <v>14640</v>
       </c>
       <c r="M12" t="n">
-        <v>180</v>
+        <v>4890</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>30930</v>
+        <v>40200</v>
       </c>
       <c r="Q12" t="n">
-        <v>1562.29</v>
+        <v>16189.84</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>540</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>690</v>
+        <v>9570</v>
       </c>
       <c r="M13" t="n">
-        <v>120</v>
+        <v>2070</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>37830</v>
+        <v>61530</v>
       </c>
       <c r="Q13" t="n">
-        <v>1326.81</v>
+        <v>13749.63</v>
       </c>
     </row>
     <row r="14">
@@ -1102,22 +1102,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1470</v>
+        <v>5610</v>
       </c>
       <c r="M14" t="n">
-        <v>840</v>
+        <v>1230</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P14" t="n">
-        <v>20160</v>
+        <v>30360</v>
       </c>
       <c r="Q14" t="n">
-        <v>1256.73</v>
+        <v>13023.35</v>
       </c>
     </row>
     <row r="15">
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>210</v>
+        <v>4230</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>19980</v>
+        <v>29280</v>
       </c>
       <c r="Q15" t="n">
-        <v>598.85</v>
+        <v>6205.78</v>
       </c>
     </row>
     <row r="16">
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>1890</v>
       </c>
       <c r="M16" t="n">
+        <v>120</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>30</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
-        <v>10470</v>
+        <v>21600</v>
       </c>
       <c r="Q16" t="n">
-        <v>245.52</v>
+        <v>2544.3</v>
       </c>
     </row>
     <row r="17">
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q17" t="n">
-        <v>45.76</v>
+        <v>474.16</v>
       </c>
     </row>
     <row r="18">
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.58</v>
+        <v>47.42</v>
       </c>
     </row>
     <row r="19">
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>180</v>
+        <v>330</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.039999999999999</v>
+        <v>83.27</v>
       </c>
     </row>
     <row r="20">
@@ -1852,7 +1852,7 @@
         <v>35160</v>
       </c>
       <c r="H4" t="n">
-        <v>4950</v>
+        <v>6450</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>104790</v>
+        <v>107400</v>
       </c>
       <c r="M4" t="n">
-        <v>10710</v>
+        <v>6030</v>
       </c>
       <c r="N4" t="n">
-        <v>720</v>
+        <v>1050</v>
       </c>
       <c r="O4" t="n">
-        <v>540</v>
+        <v>420</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1912.11</v>
+        <v>216706.14</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>35490</v>
       </c>
       <c r="H5" t="n">
-        <v>2790</v>
+        <v>3030</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>93420</v>
+        <v>105120</v>
       </c>
       <c r="M5" t="n">
-        <v>9750</v>
+        <v>12960</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O5" t="n">
-        <v>330</v>
+        <v>540</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2402.73</v>
+        <v>272309.4</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>21870</v>
       </c>
       <c r="H6" t="n">
-        <v>3600</v>
+        <v>4050</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1970,10 +1970,10 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>45180</v>
+        <v>55440</v>
       </c>
       <c r="M6" t="n">
-        <v>3450</v>
+        <v>9450</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2025.65</v>
+        <v>229573.44</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>7410</v>
       </c>
       <c r="H7" t="n">
-        <v>240</v>
+        <v>570</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>19620</v>
+        <v>27300</v>
       </c>
       <c r="M7" t="n">
-        <v>2040</v>
+        <v>5580</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1316.44</v>
+        <v>149196.42</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>7620</v>
       </c>
       <c r="H8" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2076,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8580</v>
+        <v>15930</v>
       </c>
       <c r="M8" t="n">
-        <v>900</v>
+        <v>3720</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>857.74</v>
+        <v>97210.08</v>
       </c>
     </row>
     <row r="9">
@@ -2129,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2160</v>
+        <v>5010</v>
       </c>
       <c r="M9" t="n">
-        <v>330</v>
+        <v>1560</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>335.34</v>
+        <v>38005.2</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>300</v>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2182,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4260</v>
+        <v>6030</v>
       </c>
       <c r="M10" t="n">
-        <v>2940</v>
+        <v>3960</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>156.3</v>
+        <v>17714.34</v>
       </c>
     </row>
     <row r="11">
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>780</v>
+        <v>1650</v>
       </c>
       <c r="M11" t="n">
-        <v>30</v>
+        <v>1050</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>90.26000000000001</v>
+        <v>10229.58</v>
       </c>
     </row>
     <row r="12">
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>810</v>
+        <v>1500</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.34999999999999</v>
+        <v>8880.120000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>120</v>
+        <v>1080</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>87.37</v>
+        <v>9902.16</v>
       </c>
     </row>
     <row r="14">
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>96.09</v>
+        <v>10890.54</v>
       </c>
     </row>
     <row r="15">
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.61</v>
+        <v>4262.58</v>
       </c>
     </row>
     <row r="16">
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.92</v>
+        <v>3277.26</v>
       </c>
     </row>
     <row r="17">
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1004.4</v>
+        <v>1090.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>19618.2</v>
+        <v>22075.2</v>
       </c>
       <c r="M5" t="n">
-        <v>195</v>
+        <v>259.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>120.14</v>
+        <v>13615.47</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>1093.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2052</v>
+        <v>2308.5</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -3262,10 +3262,10 @@
         <v>1.01</v>
       </c>
       <c r="L6" t="n">
-        <v>16716.6</v>
+        <v>20512.8</v>
       </c>
       <c r="M6" t="n">
-        <v>276</v>
+        <v>756</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1519.24</v>
+        <v>172180.08</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>1111.5</v>
       </c>
       <c r="H7" t="n">
-        <v>175.2</v>
+        <v>416.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>11772</v>
+        <v>16380</v>
       </c>
       <c r="M7" t="n">
-        <v>714</v>
+        <v>1953</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1053.15</v>
+        <v>119357.14</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>4953</v>
       </c>
       <c r="H8" t="n">
-        <v>76.5</v>
+        <v>127.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3368,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>6091.8</v>
+        <v>11310.3</v>
       </c>
       <c r="M8" t="n">
-        <v>495</v>
+        <v>2046</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>814.85</v>
+        <v>92349.58</v>
       </c>
     </row>
     <row r="9">
@@ -3421,10 +3421,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1749.6</v>
+        <v>4058.1</v>
       </c>
       <c r="M9" t="n">
-        <v>231</v>
+        <v>1092</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>325.28</v>
+        <v>36865.04</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>300</v>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3474,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3791.4</v>
+        <v>5366.7</v>
       </c>
       <c r="M10" t="n">
-        <v>2499</v>
+        <v>3366</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>156.3</v>
+        <v>17714.34</v>
       </c>
     </row>
     <row r="11">
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>780</v>
+        <v>1650</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>945</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>90.26000000000001</v>
+        <v>10229.58</v>
       </c>
     </row>
     <row r="12">
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>810</v>
+        <v>1500</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1083</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.34999999999999</v>
+        <v>8880.120000000001</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,10 +3633,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>120</v>
+        <v>1080</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>87.37</v>
+        <v>9902.16</v>
       </c>
     </row>
     <row r="14">
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>96.09</v>
+        <v>10890.54</v>
       </c>
     </row>
     <row r="15">
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.61</v>
+        <v>4262.58</v>
       </c>
     </row>
     <row r="16">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.92</v>
+        <v>3277.26</v>
       </c>
     </row>
     <row r="17">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5725080</v>
+        <v>6217560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>208936.47</v>
       </c>
       <c r="L5" t="n">
-        <v>3531276</v>
+        <v>3973536</v>
       </c>
       <c r="M5" t="n">
-        <v>68250</v>
+        <v>90720</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="O5" t="n">
-        <v>2805</v>
+        <v>4590</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>72081.89999999999</v>
+        <v>8169282</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>59049</v>
       </c>
       <c r="H6" t="n">
-        <v>11696400</v>
+        <v>13158450</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -4554,10 +4554,10 @@
         <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>3008988</v>
+        <v>3692304</v>
       </c>
       <c r="M6" t="n">
-        <v>96600</v>
+        <v>264600</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>911541.6</v>
+        <v>103308048</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>60021</v>
       </c>
       <c r="H7" t="n">
-        <v>998640</v>
+        <v>2371770</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2118960</v>
+        <v>2948400</v>
       </c>
       <c r="M7" t="n">
-        <v>249900</v>
+        <v>683550</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5355</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>631890.72</v>
+        <v>71614281.59999999</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>267462</v>
       </c>
       <c r="H8" t="n">
-        <v>436050</v>
+        <v>726750</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4660,10 +4660,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1096524</v>
+        <v>2035854</v>
       </c>
       <c r="M8" t="n">
-        <v>173250</v>
+        <v>716100</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>488909.52</v>
+        <v>55409745.6</v>
       </c>
     </row>
     <row r="9">
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>314928</v>
+        <v>730458</v>
       </c>
       <c r="M9" t="n">
-        <v>80850</v>
+        <v>382200</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>195167.88</v>
+        <v>22119026.4</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>16200</v>
       </c>
       <c r="H10" t="n">
-        <v>513000</v>
+        <v>1197000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4766,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>682452</v>
+        <v>966006</v>
       </c>
       <c r="M10" t="n">
-        <v>874650</v>
+        <v>1178100</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>93781.8</v>
+        <v>10628604</v>
       </c>
     </row>
     <row r="11">
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>140400</v>
+        <v>297000</v>
       </c>
       <c r="M11" t="n">
-        <v>9450</v>
+        <v>330750</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>54156.6</v>
+        <v>6137748</v>
       </c>
     </row>
     <row r="12">
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>145800</v>
+        <v>270000</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>379050</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>47012.4</v>
+        <v>5328072</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>21600</v>
+        <v>194400</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>157500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>52423.2</v>
+        <v>5941296</v>
       </c>
     </row>
     <row r="14">
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57655.8</v>
+        <v>6534324</v>
       </c>
     </row>
     <row r="15">
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>172800</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>22566.6</v>
+        <v>2557548</v>
       </c>
     </row>
     <row r="16">
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17350.2</v>
+        <v>1966356</v>
       </c>
     </row>
     <row r="17">
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>259.2</v>
+        <v>29376</v>
       </c>
     </row>
     <row r="18">
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>307.8</v>
+        <v>34884</v>
       </c>
     </row>
     <row r="19">
@@ -5728,7 +5728,7 @@
         <v>26310</v>
       </c>
       <c r="H4" t="n">
-        <v>1560</v>
+        <v>2580</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>23</v>
       </c>
       <c r="L4" t="n">
-        <v>86220</v>
+        <v>104970</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2910</v>
+        <v>3810</v>
       </c>
       <c r="O4" t="n">
-        <v>16950</v>
+        <v>20130</v>
       </c>
       <c r="P4" t="n">
-        <v>9480</v>
+        <v>8190</v>
       </c>
       <c r="Q4" t="n">
-        <v>14754.91</v>
+        <v>77657.39999999999</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>5250</v>
       </c>
       <c r="H5" t="n">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>25230</v>
+        <v>36600</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1050</v>
+        <v>1440</v>
       </c>
       <c r="O5" t="n">
-        <v>2760</v>
+        <v>5640</v>
       </c>
       <c r="P5" t="n">
-        <v>7890</v>
+        <v>11460</v>
       </c>
       <c r="Q5" t="n">
-        <v>4147.09</v>
+        <v>21826.8</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>1440</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>6270</v>
+        <v>10020</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -5855,13 +5855,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="P6" t="n">
-        <v>6000</v>
+        <v>8430</v>
       </c>
       <c r="Q6" t="n">
-        <v>236.8</v>
+        <v>1246.32</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>210</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1260</v>
+        <v>2730</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5850</v>
+        <v>9210</v>
       </c>
       <c r="Q7" t="n">
-        <v>65.05</v>
+        <v>342.36</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>210</v>
+        <v>1410</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4740</v>
+        <v>10560</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.88</v>
+        <v>183.6</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3330</v>
+        <v>9360</v>
       </c>
       <c r="Q9" t="n">
-        <v>19.7</v>
+        <v>103.68</v>
       </c>
     </row>
     <row r="10">
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.21</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>162</v>
+        <v>324</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>1.99</v>
       </c>
       <c r="L5" t="n">
-        <v>5298.3</v>
+        <v>7686</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10.5</v>
+        <v>14.4</v>
       </c>
       <c r="O5" t="n">
-        <v>138</v>
+        <v>282</v>
       </c>
       <c r="P5" t="n">
-        <v>157.8</v>
+        <v>229.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>207.35</v>
+        <v>1091.34</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>72</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>2319.9</v>
+        <v>3707.4</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -7147,13 +7147,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22.5</v>
+        <v>112.5</v>
       </c>
       <c r="P6" t="n">
-        <v>900</v>
+        <v>1264.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>177.6</v>
+        <v>934.74</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>31.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>756</v>
+        <v>1638</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1462.5</v>
+        <v>2302.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>52.04</v>
+        <v>273.89</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>149.1</v>
+        <v>1001.1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1801.2</v>
+        <v>4012.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.14</v>
+        <v>174.42</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121.5</v>
+        <v>486</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1665</v>
+        <v>4680</v>
       </c>
       <c r="Q9" t="n">
-        <v>19.11</v>
+        <v>100.57</v>
       </c>
     </row>
     <row r="10">
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>255</v>
+        <v>765</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.21</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>923400</v>
+        <v>1846800</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>96432.22</v>
       </c>
       <c r="L5" t="n">
-        <v>953694</v>
+        <v>1383480</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1785</v>
+        <v>2448</v>
       </c>
       <c r="O5" t="n">
-        <v>23460</v>
+        <v>47940</v>
       </c>
       <c r="P5" t="n">
-        <v>10257</v>
+        <v>14898</v>
       </c>
       <c r="Q5" t="n">
-        <v>124412.76</v>
+        <v>654804</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>3888</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,7 +8430,7 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>417582</v>
+        <v>667332</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -8439,13 +8439,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3825</v>
+        <v>19125</v>
       </c>
       <c r="P6" t="n">
-        <v>58500</v>
+        <v>82192.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>106560.36</v>
+        <v>560844</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>1701</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>249660</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>136080</v>
+        <v>294840</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>95062.5</v>
+        <v>149662.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>31223.23</v>
+        <v>164332.8</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26838</v>
+        <v>180198</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>117078</v>
+        <v>260832</v>
       </c>
       <c r="Q8" t="n">
-        <v>19883.88</v>
+        <v>104652</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21870</v>
+        <v>87480</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>108225</v>
+        <v>304200</v>
       </c>
       <c r="Q9" t="n">
-        <v>11464.93</v>
+        <v>60341.76</v>
       </c>
     </row>
     <row r="10">
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>16575</v>
+        <v>49725</v>
       </c>
       <c r="Q10" t="n">
-        <v>123.12</v>
+        <v>648</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>24060</v>
       </c>
       <c r="H4" t="n">
-        <v>3240</v>
+        <v>2700</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>27300</v>
+        <v>36300</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>14070</v>
+        <v>19020</v>
       </c>
       <c r="O4" t="n">
-        <v>28020</v>
+        <v>27480</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11637.28</v>
+        <v>63148.05</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>6480</v>
       </c>
       <c r="H5" t="n">
-        <v>1890</v>
+        <v>2700</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8190</v>
+        <v>9810</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4530</v>
+        <v>3480</v>
       </c>
       <c r="O5" t="n">
-        <v>30660</v>
+        <v>29100</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1558.18</v>
+        <v>8455.23</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>1770</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1380</v>
+        <v>4200</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1860</v>
+        <v>3690</v>
       </c>
       <c r="O6" t="n">
-        <v>15840</v>
+        <v>20520</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>295.36</v>
+        <v>1602.72</v>
       </c>
     </row>
     <row r="7">
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>120</v>
+        <v>1050</v>
       </c>
       <c r="O7" t="n">
-        <v>3300</v>
+        <v>6480</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>46.79</v>
+        <v>253.89</v>
       </c>
     </row>
     <row r="8">
@@ -9837,13 +9837,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>840</v>
+        <v>660</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.66</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="9">
@@ -9890,13 +9890,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.46</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>680.4</v>
+        <v>972</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1719.9</v>
+        <v>2060.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>45.3</v>
+        <v>34.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1533</v>
+        <v>1455</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>77.91</v>
+        <v>422.76</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>88.5</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>307.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>510.6</v>
+        <v>1554</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>93</v>
+        <v>184.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3960</v>
+        <v>5130</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>221.52</v>
+        <v>1202.04</v>
       </c>
     </row>
     <row r="7">
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8.4</v>
+        <v>73.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1155</v>
+        <v>2268</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.43</v>
+        <v>203.11</v>
       </c>
     </row>
     <row r="8">
@@ -11129,13 +11129,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>378</v>
+        <v>297</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.28</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="9">
@@ -11182,13 +11182,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>49.5</v>
+        <v>264</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.45</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3878280</v>
+        <v>5540400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>309582</v>
+        <v>370818</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7701</v>
+        <v>5916</v>
       </c>
       <c r="O5" t="n">
-        <v>260610</v>
+        <v>247350</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46745.34</v>
+        <v>253656.9</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>4779</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>1754460</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>91908</v>
+        <v>279720</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>15810</v>
+        <v>31365</v>
       </c>
       <c r="O6" t="n">
-        <v>673200</v>
+        <v>872100</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>132911.28</v>
+        <v>721224</v>
       </c>
     </row>
     <row r="7">
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3240</v>
+        <v>16200</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1428</v>
+        <v>12495</v>
       </c>
       <c r="O7" t="n">
-        <v>196350</v>
+        <v>385560</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>22458.38</v>
+        <v>121867.2</v>
       </c>
     </row>
     <row r="8">
@@ -12421,13 +12421,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>64260</v>
+        <v>50490</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4367.68</v>
+        <v>23700.6</v>
       </c>
     </row>
     <row r="9">
@@ -12474,13 +12474,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8415</v>
+        <v>44880</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>270.28</v>
+        <v>1466.64</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>101370</v>
       </c>
       <c r="H4" t="n">
-        <v>10770</v>
+        <v>12150</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -13492,19 +13492,19 @@
         <v>134</v>
       </c>
       <c r="L4" t="n">
-        <v>264330</v>
+        <v>254010</v>
       </c>
       <c r="M4" t="n">
-        <v>17760</v>
+        <v>4920</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>47430</v>
+        <v>47580</v>
       </c>
       <c r="P4" t="n">
-        <v>41400</v>
+        <v>11250</v>
       </c>
       <c r="Q4" t="n">
         <v>46952.02</v>
@@ -13533,7 +13533,7 @@
         <v>97650</v>
       </c>
       <c r="H5" t="n">
-        <v>11970</v>
+        <v>13050</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -13545,19 +13545,19 @@
         <v>65</v>
       </c>
       <c r="L5" t="n">
-        <v>208650</v>
+        <v>211170</v>
       </c>
       <c r="M5" t="n">
-        <v>10530</v>
+        <v>6540</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>51180</v>
+        <v>57330</v>
       </c>
       <c r="P5" t="n">
-        <v>40950</v>
+        <v>31260</v>
       </c>
       <c r="Q5" t="n">
         <v>51057.22</v>
@@ -13586,7 +13586,7 @@
         <v>41250</v>
       </c>
       <c r="H6" t="n">
-        <v>1380</v>
+        <v>1800</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -13598,19 +13598,19 @@
         <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>81210</v>
+        <v>80730</v>
       </c>
       <c r="M6" t="n">
-        <v>4200</v>
+        <v>8550</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22800</v>
+        <v>27690</v>
       </c>
       <c r="P6" t="n">
-        <v>36600</v>
+        <v>33930</v>
       </c>
       <c r="Q6" t="n">
         <v>28696.04</v>
@@ -13639,7 +13639,7 @@
         <v>10950</v>
       </c>
       <c r="H7" t="n">
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -13651,19 +13651,19 @@
         <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>36450</v>
+        <v>43920</v>
       </c>
       <c r="M7" t="n">
-        <v>2370</v>
+        <v>10530</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10890</v>
+        <v>13680</v>
       </c>
       <c r="P7" t="n">
-        <v>38670</v>
+        <v>41460</v>
       </c>
       <c r="Q7" t="n">
         <v>9425.4</v>
@@ -13692,7 +13692,7 @@
         <v>1470</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -13704,19 +13704,19 @@
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>10890</v>
+        <v>22020</v>
       </c>
       <c r="M8" t="n">
-        <v>1050</v>
+        <v>12660</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2760</v>
+        <v>4710</v>
       </c>
       <c r="P8" t="n">
-        <v>38130</v>
+        <v>41760</v>
       </c>
       <c r="Q8" t="n">
         <v>1781.25</v>
@@ -13757,19 +13757,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4050</v>
+        <v>22230</v>
       </c>
       <c r="M9" t="n">
-        <v>480</v>
+        <v>16920</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P9" t="n">
-        <v>38100</v>
+        <v>56250</v>
       </c>
       <c r="Q9" t="n">
         <v>288.15</v>
@@ -13810,19 +13810,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3060</v>
+        <v>23430</v>
       </c>
       <c r="M10" t="n">
-        <v>120</v>
+        <v>7230</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P10" t="n">
-        <v>29100</v>
+        <v>51120</v>
       </c>
       <c r="Q10" t="n">
         <v>229.67</v>
@@ -13851,7 +13851,7 @@
         <v>270</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13863,10 +13863,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3030</v>
+        <v>23460</v>
       </c>
       <c r="M11" t="n">
-        <v>450</v>
+        <v>3270</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>19830</v>
+        <v>38490</v>
       </c>
       <c r="Q11" t="n">
         <v>77.56</v>
@@ -13916,10 +13916,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1290</v>
+        <v>9690</v>
       </c>
       <c r="M12" t="n">
-        <v>150</v>
+        <v>810</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>12720</v>
+        <v>15990</v>
       </c>
       <c r="Q12" t="n">
         <v>28.46</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>210</v>
+        <v>5130</v>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>15180</v>
+        <v>31410</v>
       </c>
       <c r="Q13" t="n">
         <v>16.85</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>780</v>
+        <v>3240</v>
       </c>
       <c r="M14" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6120</v>
+        <v>15360</v>
       </c>
       <c r="Q14" t="n">
         <v>7.59</v>
@@ -14075,7 +14075,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>150</v>
+        <v>2040</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1260</v>
+        <v>3390</v>
       </c>
       <c r="Q15" t="n">
         <v>3.57</v>
@@ -14128,7 +14128,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>330</v>
+        <v>510</v>
       </c>
       <c r="Q16" t="n">
         <v>0.33</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>14569.2</v>
+        <v>16794</v>
       </c>
       <c r="I5" t="n">
         <v>0.66</v>
@@ -14837,22 +14837,22 @@
         <v>56.6</v>
       </c>
       <c r="L5" t="n">
-        <v>161324.1</v>
+        <v>180917.1</v>
       </c>
       <c r="M5" t="n">
-        <v>611.4</v>
+        <v>1005</v>
       </c>
       <c r="N5" t="n">
-        <v>142.8</v>
+        <v>189</v>
       </c>
       <c r="O5" t="n">
-        <v>8904</v>
+        <v>10186.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1548.6</v>
+        <v>1170</v>
       </c>
       <c r="Q5" t="n">
-        <v>6946.73</v>
+        <v>71988.25</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>8308.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3898.8</v>
+        <v>5147.1</v>
       </c>
       <c r="I6" t="n">
         <v>1.01</v>
@@ -14890,22 +14890,22 @@
         <v>32.45</v>
       </c>
       <c r="L6" t="n">
-        <v>128182.8</v>
+        <v>146964</v>
       </c>
       <c r="M6" t="n">
-        <v>1137.6</v>
+        <v>2884.8</v>
       </c>
       <c r="N6" t="n">
-        <v>199.5</v>
+        <v>418.5</v>
       </c>
       <c r="O6" t="n">
-        <v>21465</v>
+        <v>26497.5</v>
       </c>
       <c r="P6" t="n">
-        <v>11961</v>
+        <v>9121.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>63783.17</v>
+        <v>660978.78</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>10498.5</v>
       </c>
       <c r="H7" t="n">
-        <v>788.4</v>
+        <v>1182.6</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -14943,22 +14943,22 @@
         <v>19.14</v>
       </c>
       <c r="L7" t="n">
-        <v>106416</v>
+        <v>129798</v>
       </c>
       <c r="M7" t="n">
-        <v>3160.5</v>
+        <v>10531.5</v>
       </c>
       <c r="N7" t="n">
-        <v>18.9</v>
+        <v>102.9</v>
       </c>
       <c r="O7" t="n">
-        <v>10363.5</v>
+        <v>18690</v>
       </c>
       <c r="P7" t="n">
-        <v>21870</v>
+        <v>21180</v>
       </c>
       <c r="Q7" t="n">
-        <v>36846.57</v>
+        <v>381837.44</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>19675.5</v>
       </c>
       <c r="H8" t="n">
-        <v>153</v>
+        <v>382.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -14996,22 +14996,22 @@
         <v>8.1</v>
       </c>
       <c r="L8" t="n">
-        <v>57744.3</v>
+        <v>84582.3</v>
       </c>
       <c r="M8" t="n">
-        <v>2590.5</v>
+        <v>15015</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>3415.5</v>
+        <v>9598.5</v>
       </c>
       <c r="P8" t="n">
-        <v>30825.6</v>
+        <v>34382.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>23808.81</v>
+        <v>246728.35</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>15682.5</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>2.41</v>
       </c>
       <c r="L9" t="n">
-        <v>23619.6</v>
+        <v>52366.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2457</v>
+        <v>20328</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>396</v>
+        <v>2293.5</v>
       </c>
       <c r="P9" t="n">
-        <v>40395</v>
+        <v>59535</v>
       </c>
       <c r="Q9" t="n">
-        <v>13438.08</v>
+        <v>139257.51</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>7620</v>
       </c>
       <c r="H10" t="n">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,22 +15102,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>12602.4</v>
+        <v>40637.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3519</v>
+        <v>15861</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="P10" t="n">
-        <v>51306</v>
+        <v>88510.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>6907.48</v>
+        <v>71581.57000000001</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>1620</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15155,22 +15155,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6030</v>
+        <v>32790</v>
       </c>
       <c r="M11" t="n">
-        <v>918</v>
+        <v>5940</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="P11" t="n">
-        <v>34398</v>
+        <v>58995</v>
       </c>
       <c r="Q11" t="n">
-        <v>2824.15</v>
+        <v>29266.39</v>
       </c>
     </row>
     <row r="12">
@@ -15208,22 +15208,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2880</v>
+        <v>14640</v>
       </c>
       <c r="M12" t="n">
-        <v>171</v>
+        <v>4645.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>30930</v>
+        <v>40200</v>
       </c>
       <c r="Q12" t="n">
-        <v>1562.29</v>
+        <v>16189.84</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>540</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,10 +15261,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>690</v>
+        <v>9570</v>
       </c>
       <c r="M13" t="n">
-        <v>120</v>
+        <v>2070</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -15273,10 +15273,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>37830</v>
+        <v>61530</v>
       </c>
       <c r="Q13" t="n">
-        <v>1326.81</v>
+        <v>13749.63</v>
       </c>
     </row>
     <row r="14">
@@ -15314,22 +15314,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1470</v>
+        <v>5610</v>
       </c>
       <c r="M14" t="n">
-        <v>840</v>
+        <v>1230</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P14" t="n">
-        <v>20160</v>
+        <v>30360</v>
       </c>
       <c r="Q14" t="n">
-        <v>1256.73</v>
+        <v>13023.35</v>
       </c>
     </row>
     <row r="15">
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>210</v>
+        <v>4230</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>19980</v>
+        <v>29280</v>
       </c>
       <c r="Q15" t="n">
-        <v>598.85</v>
+        <v>6205.78</v>
       </c>
     </row>
     <row r="16">
@@ -15420,22 +15420,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>1890</v>
       </c>
       <c r="M16" t="n">
+        <v>120</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>30</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
-        <v>10470</v>
+        <v>21600</v>
       </c>
       <c r="Q16" t="n">
-        <v>245.52</v>
+        <v>2544.3</v>
       </c>
     </row>
     <row r="17">
@@ -15473,10 +15473,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -15485,10 +15485,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q17" t="n">
-        <v>45.76</v>
+        <v>474.16</v>
       </c>
     </row>
     <row r="18">
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15541,7 +15541,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.58</v>
+        <v>47.42</v>
       </c>
     </row>
     <row r="19">
@@ -15582,7 +15582,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>180</v>
+        <v>330</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.039999999999999</v>
+        <v>83.27</v>
       </c>
     </row>
     <row r="20">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4309.2</v>
+        <v>4698</v>
       </c>
       <c r="I5" t="n">
         <v>0.66</v>
@@ -16129,19 +16129,19 @@
         <v>21.52</v>
       </c>
       <c r="L5" t="n">
-        <v>43816.5</v>
+        <v>44345.7</v>
       </c>
       <c r="M5" t="n">
-        <v>210.6</v>
+        <v>130.8</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2559</v>
+        <v>2866.5</v>
       </c>
       <c r="P5" t="n">
-        <v>819</v>
+        <v>625.2</v>
       </c>
       <c r="Q5" t="n">
         <v>2552.86</v>
@@ -16170,7 +16170,7 @@
         <v>2062.5</v>
       </c>
       <c r="H6" t="n">
-        <v>786.6</v>
+        <v>1026</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -16182,19 +16182,19 @@
         <v>12.17</v>
       </c>
       <c r="L6" t="n">
-        <v>30047.7</v>
+        <v>29870.1</v>
       </c>
       <c r="M6" t="n">
-        <v>336</v>
+        <v>684</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5700</v>
+        <v>6922.5</v>
       </c>
       <c r="P6" t="n">
-        <v>5490</v>
+        <v>5089.5</v>
       </c>
       <c r="Q6" t="n">
         <v>21522.03</v>
@@ -16223,7 +16223,7 @@
         <v>1642.5</v>
       </c>
       <c r="H7" t="n">
-        <v>306.6</v>
+        <v>372.3</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -16235,19 +16235,19 @@
         <v>2.55</v>
       </c>
       <c r="L7" t="n">
-        <v>21870</v>
+        <v>26352</v>
       </c>
       <c r="M7" t="n">
-        <v>829.5</v>
+        <v>3685.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3811.5</v>
+        <v>4788</v>
       </c>
       <c r="P7" t="n">
-        <v>9667.5</v>
+        <v>10365</v>
       </c>
       <c r="Q7" t="n">
         <v>7540.32</v>
@@ -16276,7 +16276,7 @@
         <v>955.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16288,19 +16288,19 @@
         <v>2.94</v>
       </c>
       <c r="L8" t="n">
-        <v>7731.9</v>
+        <v>15634.2</v>
       </c>
       <c r="M8" t="n">
-        <v>577.5</v>
+        <v>6963</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1242</v>
+        <v>2119.5</v>
       </c>
       <c r="P8" t="n">
-        <v>14489.4</v>
+        <v>15868.8</v>
       </c>
       <c r="Q8" t="n">
         <v>1692.19</v>
@@ -16341,19 +16341,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3280.5</v>
+        <v>18006.3</v>
       </c>
       <c r="M9" t="n">
-        <v>336</v>
+        <v>11844</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16.5</v>
+        <v>66</v>
       </c>
       <c r="P9" t="n">
-        <v>19050</v>
+        <v>28125</v>
       </c>
       <c r="Q9" t="n">
         <v>279.51</v>
@@ -16394,19 +16394,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2723.4</v>
+        <v>20852.7</v>
       </c>
       <c r="M10" t="n">
-        <v>102</v>
+        <v>6145.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P10" t="n">
-        <v>24735</v>
+        <v>43452</v>
       </c>
       <c r="Q10" t="n">
         <v>229.67</v>
@@ -16435,7 +16435,7 @@
         <v>270</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -16447,10 +16447,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3030</v>
+        <v>23460</v>
       </c>
       <c r="M11" t="n">
-        <v>405</v>
+        <v>2943</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>17847</v>
+        <v>34641</v>
       </c>
       <c r="Q11" t="n">
         <v>77.56</v>
@@ -16500,10 +16500,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1290</v>
+        <v>9690</v>
       </c>
       <c r="M12" t="n">
-        <v>142.5</v>
+        <v>769.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>12720</v>
+        <v>15990</v>
       </c>
       <c r="Q12" t="n">
         <v>28.46</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>210</v>
+        <v>5130</v>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>15180</v>
+        <v>31410</v>
       </c>
       <c r="Q13" t="n">
         <v>16.85</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>780</v>
+        <v>3240</v>
       </c>
       <c r="M14" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6120</v>
+        <v>15360</v>
       </c>
       <c r="Q14" t="n">
         <v>7.59</v>
@@ -16659,7 +16659,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>150</v>
+        <v>2040</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1260</v>
+        <v>3390</v>
       </c>
       <c r="Q15" t="n">
         <v>3.57</v>
@@ -16712,7 +16712,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>330</v>
+        <v>510</v>
       </c>
       <c r="Q16" t="n">
         <v>0.33</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>24562440</v>
+        <v>26778600</v>
       </c>
       <c r="I5" t="n">
         <v>128576.29</v>
@@ -17421,19 +17421,19 @@
         <v>1044682.34</v>
       </c>
       <c r="L5" t="n">
-        <v>7886970</v>
+        <v>7982226</v>
       </c>
       <c r="M5" t="n">
-        <v>73710</v>
+        <v>45780</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>435030</v>
+        <v>487305</v>
       </c>
       <c r="P5" t="n">
-        <v>53235</v>
+        <v>40638</v>
       </c>
       <c r="Q5" t="n">
         <v>1531716.7</v>
@@ -17462,7 +17462,7 @@
         <v>111375</v>
       </c>
       <c r="H6" t="n">
-        <v>4483620</v>
+        <v>5848200</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -17474,19 +17474,19 @@
         <v>590829.41</v>
       </c>
       <c r="L6" t="n">
-        <v>5408586</v>
+        <v>5376618</v>
       </c>
       <c r="M6" t="n">
-        <v>117600</v>
+        <v>239400</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>969000</v>
+        <v>1176825</v>
       </c>
       <c r="P6" t="n">
-        <v>356850</v>
+        <v>330817.5</v>
       </c>
       <c r="Q6" t="n">
         <v>12913219.26</v>
@@ -17515,7 +17515,7 @@
         <v>88695</v>
       </c>
       <c r="H7" t="n">
-        <v>1747620</v>
+        <v>2122110</v>
       </c>
       <c r="I7" t="n">
         <v>123914.91</v>
@@ -17527,19 +17527,19 @@
         <v>123914.91</v>
       </c>
       <c r="L7" t="n">
-        <v>3936600</v>
+        <v>4743360</v>
       </c>
       <c r="M7" t="n">
-        <v>290325</v>
+        <v>1289925</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>647955</v>
+        <v>813960</v>
       </c>
       <c r="P7" t="n">
-        <v>628387.5</v>
+        <v>673725</v>
       </c>
       <c r="Q7" t="n">
         <v>4524192.58</v>
@@ -17568,7 +17568,7 @@
         <v>51597</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>581400</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -17580,19 +17580,19 @@
         <v>142948.86</v>
       </c>
       <c r="L8" t="n">
-        <v>1391742</v>
+        <v>2814156</v>
       </c>
       <c r="M8" t="n">
-        <v>202125</v>
+        <v>2437050</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>211140</v>
+        <v>360315</v>
       </c>
       <c r="P8" t="n">
-        <v>941811</v>
+        <v>1031472</v>
       </c>
       <c r="Q8" t="n">
         <v>1015311.13</v>
@@ -17633,19 +17633,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>590490</v>
+        <v>3241134</v>
       </c>
       <c r="M9" t="n">
-        <v>117600</v>
+        <v>4145400</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2805</v>
+        <v>11220</v>
       </c>
       <c r="P9" t="n">
-        <v>1238250</v>
+        <v>1828125</v>
       </c>
       <c r="Q9" t="n">
         <v>167704</v>
@@ -17686,19 +17686,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>490212</v>
+        <v>3753486</v>
       </c>
       <c r="M10" t="n">
-        <v>35700</v>
+        <v>2150925</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3570</v>
       </c>
       <c r="P10" t="n">
-        <v>1607775</v>
+        <v>2824380</v>
       </c>
       <c r="Q10" t="n">
         <v>137803.68</v>
@@ -17727,7 +17727,7 @@
         <v>14580</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -17739,10 +17739,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>545400</v>
+        <v>4222800</v>
       </c>
       <c r="M11" t="n">
-        <v>141750</v>
+        <v>1030050</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1160055</v>
+        <v>2251665</v>
       </c>
       <c r="Q11" t="n">
         <v>46537.2</v>
@@ -17792,10 +17792,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>232200</v>
+        <v>1744200</v>
       </c>
       <c r="M12" t="n">
-        <v>49875</v>
+        <v>269325</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -17804,7 +17804,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>826800</v>
+        <v>1039350</v>
       </c>
       <c r="Q12" t="n">
         <v>17074.8</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>37800</v>
+        <v>923400</v>
       </c>
       <c r="M13" t="n">
-        <v>10500</v>
+        <v>84000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>986700</v>
+        <v>2041650</v>
       </c>
       <c r="Q13" t="n">
         <v>10110.96</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>140400</v>
+        <v>583200</v>
       </c>
       <c r="M14" t="n">
-        <v>105000</v>
+        <v>147000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>397800</v>
+        <v>998400</v>
       </c>
       <c r="Q14" t="n">
         <v>4553.28</v>
@@ -17951,7 +17951,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>27000</v>
+        <v>367200</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>81900</v>
+        <v>220350</v>
       </c>
       <c r="Q15" t="n">
         <v>2142.72</v>
@@ -18004,7 +18004,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>21450</v>
+        <v>33150</v>
       </c>
       <c r="Q16" t="n">
         <v>200.88</v>
@@ -18648,7 +18648,7 @@
         <v>50220</v>
       </c>
       <c r="H4" t="n">
-        <v>3990</v>
+        <v>4710</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>179070</v>
+        <v>217200</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2850</v>
+        <v>3060</v>
       </c>
       <c r="O4" t="n">
-        <v>43860</v>
+        <v>52350</v>
       </c>
       <c r="P4" t="n">
-        <v>5280</v>
+        <v>3180</v>
       </c>
       <c r="Q4" t="n">
-        <v>16182.2</v>
+        <v>185421.06</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>10050</v>
       </c>
       <c r="H5" t="n">
-        <v>1050</v>
+        <v>1440</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>46860</v>
+        <v>64200</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>600</v>
+        <v>1470</v>
       </c>
       <c r="O5" t="n">
-        <v>17850</v>
+        <v>25560</v>
       </c>
       <c r="P5" t="n">
-        <v>3810</v>
+        <v>6390</v>
       </c>
       <c r="Q5" t="n">
-        <v>3451.59</v>
+        <v>39549.51</v>
       </c>
     </row>
     <row r="6">
@@ -18754,34 +18754,34 @@
         <v>840</v>
       </c>
       <c r="H6" t="n">
+        <v>270</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>14910</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>210</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8790</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" t="n">
-        <v>2820</v>
+        <v>4380</v>
       </c>
       <c r="P6" t="n">
-        <v>2640</v>
+        <v>5820</v>
       </c>
       <c r="Q6" t="n">
-        <v>291.77</v>
+        <v>3343.23</v>
       </c>
     </row>
     <row r="7">
@@ -18819,7 +18819,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>540</v>
+        <v>2100</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -18828,13 +18828,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P7" t="n">
-        <v>3030</v>
+        <v>7980</v>
       </c>
       <c r="Q7" t="n">
-        <v>76.45999999999999</v>
+        <v>876.15</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>540</v>
+        <v>2070</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.59</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="9">
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>378</v>
+        <v>518.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>3.31</v>
       </c>
       <c r="L5" t="n">
-        <v>9840.6</v>
+        <v>13482</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>14.7</v>
       </c>
       <c r="O5" t="n">
-        <v>892.5</v>
+        <v>1278</v>
       </c>
       <c r="P5" t="n">
-        <v>76.2</v>
+        <v>127.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.58</v>
+        <v>1977.48</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>42</v>
       </c>
       <c r="H6" t="n">
-        <v>119.7</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3252.3</v>
+        <v>5516.7</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O6" t="n">
-        <v>705</v>
+        <v>1095</v>
       </c>
       <c r="P6" t="n">
-        <v>396</v>
+        <v>873</v>
       </c>
       <c r="Q6" t="n">
-        <v>218.83</v>
+        <v>2507.42</v>
       </c>
     </row>
     <row r="7">
@@ -20111,7 +20111,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>324</v>
+        <v>1260</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -20120,13 +20120,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="P7" t="n">
-        <v>757.5</v>
+        <v>1995</v>
       </c>
       <c r="Q7" t="n">
-        <v>61.17</v>
+        <v>700.92</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>63.9</v>
+        <v>170.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>205.2</v>
+        <v>786.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="9">
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2154600</v>
+        <v>2954880</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>160720.36</v>
       </c>
       <c r="L5" t="n">
-        <v>1771308</v>
+        <v>2426760</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1020</v>
+        <v>2499</v>
       </c>
       <c r="O5" t="n">
-        <v>151725</v>
+        <v>217260</v>
       </c>
       <c r="P5" t="n">
-        <v>4953</v>
+        <v>8307</v>
       </c>
       <c r="Q5" t="n">
-        <v>103547.81</v>
+        <v>1186485.3</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>2268</v>
       </c>
       <c r="H6" t="n">
-        <v>682290</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>585414</v>
+        <v>993006</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1785</v>
       </c>
       <c r="O6" t="n">
-        <v>119850</v>
+        <v>186150</v>
       </c>
       <c r="P6" t="n">
-        <v>25740</v>
+        <v>56745</v>
       </c>
       <c r="Q6" t="n">
-        <v>131297.76</v>
+        <v>1504453.5</v>
       </c>
     </row>
     <row r="7">
@@ -21403,7 +21403,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>58320</v>
+        <v>226800</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -21412,13 +21412,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1785</v>
+        <v>7140</v>
       </c>
       <c r="P7" t="n">
-        <v>49237.5</v>
+        <v>129675</v>
       </c>
       <c r="Q7" t="n">
-        <v>36702.72</v>
+        <v>420552</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>11502</v>
+        <v>30672</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>13338</v>
+        <v>51129</v>
       </c>
       <c r="Q8" t="n">
-        <v>1477.44</v>
+        <v>16929</v>
       </c>
     </row>
     <row r="9">
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>16200</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>83044440</v>
+        <v>95725800</v>
       </c>
       <c r="I5" t="n">
         <v>128576.29</v>
@@ -22589,22 +22589,22 @@
         <v>2748318.16</v>
       </c>
       <c r="L5" t="n">
-        <v>29038338</v>
+        <v>32565078</v>
       </c>
       <c r="M5" t="n">
-        <v>213990</v>
+        <v>351750</v>
       </c>
       <c r="N5" t="n">
-        <v>24276</v>
+        <v>32130</v>
       </c>
       <c r="O5" t="n">
-        <v>1513680</v>
+        <v>1731705</v>
       </c>
       <c r="P5" t="n">
-        <v>100659</v>
+        <v>76050</v>
       </c>
       <c r="Q5" t="n">
-        <v>4168035.68</v>
+        <v>43192950.44</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>448659</v>
       </c>
       <c r="H6" t="n">
-        <v>22223160</v>
+        <v>29338470</v>
       </c>
       <c r="I6" t="n">
         <v>196943.14</v>
@@ -22642,22 +22642,22 @@
         <v>1575545.09</v>
       </c>
       <c r="L6" t="n">
-        <v>23072904</v>
+        <v>26453520</v>
       </c>
       <c r="M6" t="n">
-        <v>398160</v>
+        <v>1009680</v>
       </c>
       <c r="N6" t="n">
-        <v>33915</v>
+        <v>71145</v>
       </c>
       <c r="O6" t="n">
-        <v>3649050</v>
+        <v>4504575</v>
       </c>
       <c r="P6" t="n">
-        <v>777465</v>
+        <v>592897.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>38269899.9</v>
+        <v>396587269.12</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>566919</v>
       </c>
       <c r="H7" t="n">
-        <v>4493880</v>
+        <v>6740820</v>
       </c>
       <c r="I7" t="n">
         <v>123914.91</v>
@@ -22695,22 +22695,22 @@
         <v>929361.84</v>
       </c>
       <c r="L7" t="n">
-        <v>19154880</v>
+        <v>23363640</v>
       </c>
       <c r="M7" t="n">
-        <v>1106175</v>
+        <v>3686025</v>
       </c>
       <c r="N7" t="n">
-        <v>3213</v>
+        <v>17493</v>
       </c>
       <c r="O7" t="n">
-        <v>1761795</v>
+        <v>3177300</v>
       </c>
       <c r="P7" t="n">
-        <v>1421550</v>
+        <v>1376700</v>
       </c>
       <c r="Q7" t="n">
-        <v>22107942.14</v>
+        <v>229102464.96</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>1062477</v>
       </c>
       <c r="H8" t="n">
-        <v>872100</v>
+        <v>2180250</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22748,22 +22748,22 @@
         <v>393109.38</v>
       </c>
       <c r="L8" t="n">
-        <v>10393974</v>
+        <v>15224814</v>
       </c>
       <c r="M8" t="n">
-        <v>906675</v>
+        <v>5255250</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O8" t="n">
-        <v>580635</v>
+        <v>1631745</v>
       </c>
       <c r="P8" t="n">
-        <v>2003664</v>
+        <v>2234856</v>
       </c>
       <c r="Q8" t="n">
-        <v>14285283.23</v>
+        <v>148037007.64</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>846855</v>
       </c>
       <c r="H9" t="n">
-        <v>513000</v>
+        <v>1881000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>116971.4</v>
       </c>
       <c r="L9" t="n">
-        <v>4251528</v>
+        <v>9425970</v>
       </c>
       <c r="M9" t="n">
-        <v>859950</v>
+        <v>7114800</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>67320</v>
+        <v>389895</v>
       </c>
       <c r="P9" t="n">
-        <v>2625675</v>
+        <v>3869775</v>
       </c>
       <c r="Q9" t="n">
-        <v>8062847.11</v>
+        <v>83554504.37</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>411480</v>
       </c>
       <c r="H10" t="n">
-        <v>855000</v>
+        <v>2394000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2268432</v>
+        <v>7314732</v>
       </c>
       <c r="M10" t="n">
-        <v>1231650</v>
+        <v>5551350</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>57120</v>
       </c>
       <c r="P10" t="n">
-        <v>3334890</v>
+        <v>5753182.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4144489.2</v>
+        <v>42948940.5</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>87480</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22907,22 +22907,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1085400</v>
+        <v>5902200</v>
       </c>
       <c r="M11" t="n">
-        <v>321300</v>
+        <v>2079000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>8670</v>
       </c>
       <c r="P11" t="n">
-        <v>2235870</v>
+        <v>3834675</v>
       </c>
       <c r="Q11" t="n">
-        <v>1694489.76</v>
+        <v>17559833.4</v>
       </c>
     </row>
     <row r="12">
@@ -22960,22 +22960,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>518400</v>
+        <v>2635200</v>
       </c>
       <c r="M12" t="n">
-        <v>59850</v>
+        <v>1625925</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P12" t="n">
-        <v>2010450</v>
+        <v>2613000</v>
       </c>
       <c r="Q12" t="n">
-        <v>937373.04</v>
+        <v>9713906.1</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>29160</v>
       </c>
       <c r="H13" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,10 +23013,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>124200</v>
+        <v>1722600</v>
       </c>
       <c r="M13" t="n">
-        <v>42000</v>
+        <v>724500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2458950</v>
+        <v>3999450</v>
       </c>
       <c r="Q13" t="n">
-        <v>796087.4399999999</v>
+        <v>8249777.1</v>
       </c>
     </row>
     <row r="14">
@@ -23066,22 +23066,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>264600</v>
+        <v>1009800</v>
       </c>
       <c r="M14" t="n">
-        <v>294000</v>
+        <v>430500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P14" t="n">
-        <v>1310400</v>
+        <v>1973400</v>
       </c>
       <c r="Q14" t="n">
-        <v>754036.5600000001</v>
+        <v>7814007.9</v>
       </c>
     </row>
     <row r="15">
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>37800</v>
+        <v>761400</v>
       </c>
       <c r="M15" t="n">
-        <v>52500</v>
+        <v>105000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P15" t="n">
-        <v>1298700</v>
+        <v>1903200</v>
       </c>
       <c r="Q15" t="n">
-        <v>359307.36</v>
+        <v>3723467.4</v>
       </c>
     </row>
     <row r="16">
@@ -23172,22 +23172,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10800</v>
+        <v>340200</v>
       </c>
       <c r="M16" t="n">
-        <v>10500</v>
+        <v>42000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="P16" t="n">
-        <v>680550</v>
+        <v>1404000</v>
       </c>
       <c r="Q16" t="n">
-        <v>147312</v>
+        <v>1526580</v>
       </c>
     </row>
     <row r="17">
@@ -23225,10 +23225,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -23237,10 +23237,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="Q17" t="n">
-        <v>27453.6</v>
+        <v>284499</v>
       </c>
     </row>
     <row r="18">
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23293,7 +23293,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2745.36</v>
+        <v>28449.9</v>
       </c>
     </row>
     <row r="19">
@@ -23334,7 +23334,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>63000</v>
+        <v>115500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4821.12</v>
+        <v>49960.8</v>
       </c>
     </row>
     <row r="20">
@@ -23816,7 +23816,7 @@
         <v>102600</v>
       </c>
       <c r="H4" t="n">
-        <v>6090</v>
+        <v>7710</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -23828,22 +23828,22 @@
         <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>258270</v>
+        <v>282660</v>
       </c>
       <c r="M4" t="n">
-        <v>24270</v>
+        <v>46020</v>
       </c>
       <c r="N4" t="n">
-        <v>14490</v>
+        <v>19590</v>
       </c>
       <c r="O4" t="n">
-        <v>24780</v>
+        <v>28140</v>
       </c>
       <c r="P4" t="n">
-        <v>5970</v>
+        <v>3420</v>
       </c>
       <c r="Q4" t="n">
-        <v>32404.21</v>
+        <v>317688.3</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>81630</v>
       </c>
       <c r="H5" t="n">
-        <v>1440</v>
+        <v>1890</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>59</v>
       </c>
       <c r="L5" t="n">
-        <v>214410</v>
+        <v>245730</v>
       </c>
       <c r="M5" t="n">
-        <v>6090</v>
+        <v>27150</v>
       </c>
       <c r="N5" t="n">
-        <v>3270</v>
+        <v>4590</v>
       </c>
       <c r="O5" t="n">
-        <v>25410</v>
+        <v>28680</v>
       </c>
       <c r="P5" t="n">
-        <v>9930</v>
+        <v>6660</v>
       </c>
       <c r="Q5" t="n">
-        <v>34764.57</v>
+        <v>340829.1</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>74340</v>
       </c>
       <c r="H6" t="n">
-        <v>30</v>
+        <v>360</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>36</v>
       </c>
       <c r="L6" t="n">
-        <v>141300</v>
+        <v>160350</v>
       </c>
       <c r="M6" t="n">
-        <v>4200</v>
+        <v>13920</v>
       </c>
       <c r="N6" t="n">
-        <v>870</v>
+        <v>1770</v>
       </c>
       <c r="O6" t="n">
-        <v>21570</v>
+        <v>26640</v>
       </c>
       <c r="P6" t="n">
-        <v>13620</v>
+        <v>8100</v>
       </c>
       <c r="Q6" t="n">
-        <v>27675.59</v>
+        <v>271329.3</v>
       </c>
     </row>
     <row r="7">
@@ -23987,22 +23987,22 @@
         <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>93300</v>
+        <v>107730</v>
       </c>
       <c r="M7" t="n">
-        <v>3030</v>
+        <v>6960</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O7" t="n">
-        <v>7890</v>
+        <v>16590</v>
       </c>
       <c r="P7" t="n">
-        <v>16620</v>
+        <v>12180</v>
       </c>
       <c r="Q7" t="n">
-        <v>19071.45</v>
+        <v>186975</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>16890</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>51600</v>
+        <v>65370</v>
       </c>
       <c r="M8" t="n">
-        <v>1920</v>
+        <v>5220</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2310</v>
+        <v>10500</v>
       </c>
       <c r="P8" t="n">
-        <v>14610</v>
+        <v>14910</v>
       </c>
       <c r="Q8" t="n">
-        <v>12261.08</v>
+        <v>120206.7</v>
       </c>
     </row>
     <row r="9">
@@ -24093,22 +24093,22 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>19920</v>
+        <v>30150</v>
       </c>
       <c r="M9" t="n">
-        <v>2550</v>
+        <v>4590</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>450</v>
+        <v>1980</v>
       </c>
       <c r="P9" t="n">
-        <v>14970</v>
+        <v>12840</v>
       </c>
       <c r="Q9" t="n">
-        <v>7621.33</v>
+        <v>74718.89999999999</v>
       </c>
     </row>
     <row r="10">
@@ -24146,22 +24146,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5640</v>
+        <v>10830</v>
       </c>
       <c r="M10" t="n">
-        <v>780</v>
+        <v>3990</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="P10" t="n">
-        <v>16290</v>
+        <v>21360</v>
       </c>
       <c r="Q10" t="n">
-        <v>3663.65</v>
+        <v>35918.1</v>
       </c>
     </row>
     <row r="11">
@@ -24199,22 +24199,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1770</v>
+        <v>5190</v>
       </c>
       <c r="M11" t="n">
-        <v>510</v>
+        <v>1350</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
-        <v>12150</v>
+        <v>14820</v>
       </c>
       <c r="Q11" t="n">
-        <v>1194.13</v>
+        <v>11707.2</v>
       </c>
     </row>
     <row r="12">
@@ -24252,7 +24252,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>690</v>
+        <v>2970</v>
       </c>
       <c r="M12" t="n">
         <v>30</v>
@@ -24261,13 +24261,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>11070</v>
+        <v>9450</v>
       </c>
       <c r="Q12" t="n">
-        <v>429.26</v>
+        <v>4208.4</v>
       </c>
     </row>
     <row r="13">
@@ -24305,10 +24305,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>210</v>
+        <v>3240</v>
       </c>
       <c r="M13" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -24317,10 +24317,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>19950</v>
+        <v>24810</v>
       </c>
       <c r="Q13" t="n">
-        <v>232.99</v>
+        <v>2284.2</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>150</v>
+        <v>960</v>
       </c>
       <c r="M14" t="n">
-        <v>540</v>
+        <v>660</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P14" t="n">
-        <v>13440</v>
+        <v>13860</v>
       </c>
       <c r="Q14" t="n">
-        <v>155.97</v>
+        <v>1529.1</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M15" t="n">
         <v>60</v>
       </c>
-      <c r="M15" t="n">
-        <v>150</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>18720</v>
+        <v>25890</v>
       </c>
       <c r="Q15" t="n">
-        <v>112.64</v>
+        <v>1104.3</v>
       </c>
     </row>
     <row r="16">
@@ -24464,22 +24464,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>1290</v>
       </c>
       <c r="M16" t="n">
+        <v>120</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>30</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
-        <v>10140</v>
+        <v>21090</v>
       </c>
       <c r="Q16" t="n">
-        <v>58.57</v>
+        <v>574.2</v>
       </c>
     </row>
     <row r="17">
@@ -24520,7 +24520,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -24529,10 +24529,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.71</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -24573,7 +24573,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24585,7 +24585,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.73</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="19">
@@ -24626,7 +24626,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>180</v>
+        <v>330</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -24638,7 +24638,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>518.4</v>
+        <v>680.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>19.53</v>
       </c>
       <c r="L5" t="n">
-        <v>45026.1</v>
+        <v>51603.3</v>
       </c>
       <c r="M5" t="n">
-        <v>121.8</v>
+        <v>543</v>
       </c>
       <c r="N5" t="n">
-        <v>32.7</v>
+        <v>45.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1270.5</v>
+        <v>1434</v>
       </c>
       <c r="P5" t="n">
-        <v>198.6</v>
+        <v>133.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1738.23</v>
+        <v>17041.46</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3717</v>
       </c>
       <c r="H6" t="n">
-        <v>17.1</v>
+        <v>205.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>18.25</v>
       </c>
       <c r="L6" t="n">
-        <v>52281</v>
+        <v>59329.5</v>
       </c>
       <c r="M6" t="n">
-        <v>336</v>
+        <v>1113.6</v>
       </c>
       <c r="N6" t="n">
-        <v>43.5</v>
+        <v>88.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5392.5</v>
+        <v>6660</v>
       </c>
       <c r="P6" t="n">
-        <v>2043</v>
+        <v>1215</v>
       </c>
       <c r="Q6" t="n">
-        <v>20756.69</v>
+        <v>203496.97</v>
       </c>
     </row>
     <row r="7">
@@ -25279,22 +25279,22 @@
         <v>16.59</v>
       </c>
       <c r="L7" t="n">
-        <v>55980</v>
+        <v>64638</v>
       </c>
       <c r="M7" t="n">
-        <v>1060.5</v>
+        <v>2436</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>2761.5</v>
+        <v>5806.5</v>
       </c>
       <c r="P7" t="n">
-        <v>4155</v>
+        <v>3045</v>
       </c>
       <c r="Q7" t="n">
-        <v>15257.16</v>
+        <v>149580</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>10978.5</v>
       </c>
       <c r="H8" t="n">
-        <v>25.5</v>
+        <v>76.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>5.15</v>
       </c>
       <c r="L8" t="n">
-        <v>36636</v>
+        <v>46412.7</v>
       </c>
       <c r="M8" t="n">
-        <v>1056</v>
+        <v>2871</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1039.5</v>
+        <v>4725</v>
       </c>
       <c r="P8" t="n">
-        <v>5551.8</v>
+        <v>5665.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>11648.03</v>
+        <v>114196.36</v>
       </c>
     </row>
     <row r="9">
@@ -25385,22 +25385,22 @@
         <v>1.61</v>
       </c>
       <c r="L9" t="n">
-        <v>16135.2</v>
+        <v>24421.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1785</v>
+        <v>3213</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>247.5</v>
+        <v>1089</v>
       </c>
       <c r="P9" t="n">
-        <v>7485</v>
+        <v>6420</v>
       </c>
       <c r="Q9" t="n">
-        <v>7392.69</v>
+        <v>72477.33</v>
       </c>
     </row>
     <row r="10">
@@ -25438,22 +25438,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5019.6</v>
+        <v>9638.700000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>663</v>
+        <v>3391.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="P10" t="n">
-        <v>13846.5</v>
+        <v>18156</v>
       </c>
       <c r="Q10" t="n">
-        <v>3663.65</v>
+        <v>35918.1</v>
       </c>
     </row>
     <row r="11">
@@ -25491,22 +25491,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1770</v>
+        <v>5190</v>
       </c>
       <c r="M11" t="n">
-        <v>459</v>
+        <v>1215</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="P11" t="n">
-        <v>10935</v>
+        <v>13338</v>
       </c>
       <c r="Q11" t="n">
-        <v>1194.13</v>
+        <v>11707.2</v>
       </c>
     </row>
     <row r="12">
@@ -25544,7 +25544,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>690</v>
+        <v>2970</v>
       </c>
       <c r="M12" t="n">
         <v>28.5</v>
@@ -25553,13 +25553,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>11070</v>
+        <v>9450</v>
       </c>
       <c r="Q12" t="n">
-        <v>429.26</v>
+        <v>4208.4</v>
       </c>
     </row>
     <row r="13">
@@ -25597,10 +25597,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>210</v>
+        <v>3240</v>
       </c>
       <c r="M13" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -25609,10 +25609,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>19950</v>
+        <v>24810</v>
       </c>
       <c r="Q13" t="n">
-        <v>232.99</v>
+        <v>2284.2</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>150</v>
+        <v>960</v>
       </c>
       <c r="M14" t="n">
-        <v>540</v>
+        <v>660</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P14" t="n">
-        <v>13440</v>
+        <v>13860</v>
       </c>
       <c r="Q14" t="n">
-        <v>155.97</v>
+        <v>1529.1</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M15" t="n">
         <v>60</v>
       </c>
-      <c r="M15" t="n">
-        <v>150</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>18720</v>
+        <v>25890</v>
       </c>
       <c r="Q15" t="n">
-        <v>112.64</v>
+        <v>1104.3</v>
       </c>
     </row>
     <row r="16">
@@ -25756,22 +25756,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>1290</v>
       </c>
       <c r="M16" t="n">
+        <v>120</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>30</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
-        <v>10140</v>
+        <v>21090</v>
       </c>
       <c r="Q16" t="n">
-        <v>58.57</v>
+        <v>574.2</v>
       </c>
     </row>
     <row r="17">
@@ -25812,7 +25812,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -25821,10 +25821,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.71</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -25865,7 +25865,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25877,7 +25877,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.73</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="19">
@@ -25918,7 +25918,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>180</v>
+        <v>330</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -25930,7 +25930,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2954880</v>
+        <v>3878280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>948250.12</v>
       </c>
       <c r="L5" t="n">
-        <v>8104698</v>
+        <v>9288594</v>
       </c>
       <c r="M5" t="n">
-        <v>42630</v>
+        <v>190050</v>
       </c>
       <c r="N5" t="n">
-        <v>5559</v>
+        <v>7803</v>
       </c>
       <c r="O5" t="n">
-        <v>215985</v>
+        <v>243780</v>
       </c>
       <c r="P5" t="n">
-        <v>12909</v>
+        <v>8658</v>
       </c>
       <c r="Q5" t="n">
-        <v>1042937.05</v>
+        <v>10224873</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>200718</v>
       </c>
       <c r="H6" t="n">
-        <v>97470</v>
+        <v>1169640</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>886244.11</v>
       </c>
       <c r="L6" t="n">
-        <v>9410580</v>
+        <v>10679310</v>
       </c>
       <c r="M6" t="n">
-        <v>117600</v>
+        <v>389760</v>
       </c>
       <c r="N6" t="n">
-        <v>7395</v>
+        <v>15045</v>
       </c>
       <c r="O6" t="n">
-        <v>916725</v>
+        <v>1132200</v>
       </c>
       <c r="P6" t="n">
-        <v>132795</v>
+        <v>78975</v>
       </c>
       <c r="Q6" t="n">
-        <v>12454014.87</v>
+        <v>122098185</v>
       </c>
     </row>
     <row r="7">
@@ -26571,22 +26571,22 @@
         <v>805446.9300000001</v>
       </c>
       <c r="L7" t="n">
-        <v>10076400</v>
+        <v>11634840</v>
       </c>
       <c r="M7" t="n">
-        <v>371175</v>
+        <v>852600</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="O7" t="n">
-        <v>469455</v>
+        <v>987105</v>
       </c>
       <c r="P7" t="n">
-        <v>270075</v>
+        <v>197925</v>
       </c>
       <c r="Q7" t="n">
-        <v>9154296</v>
+        <v>89748000</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>592839</v>
       </c>
       <c r="H8" t="n">
-        <v>145350</v>
+        <v>436050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>250160.51</v>
       </c>
       <c r="L8" t="n">
-        <v>6594480</v>
+        <v>8354286</v>
       </c>
       <c r="M8" t="n">
-        <v>369600</v>
+        <v>1004850</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>176715</v>
+        <v>803250</v>
       </c>
       <c r="P8" t="n">
-        <v>360867</v>
+        <v>368277</v>
       </c>
       <c r="Q8" t="n">
-        <v>6988817.54</v>
+        <v>68517819</v>
       </c>
     </row>
     <row r="9">
@@ -26677,22 +26677,22 @@
         <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>2904336</v>
+        <v>4395870</v>
       </c>
       <c r="M9" t="n">
-        <v>624750</v>
+        <v>1124550</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>42075</v>
+        <v>185130</v>
       </c>
       <c r="P9" t="n">
-        <v>486525</v>
+        <v>417300</v>
       </c>
       <c r="Q9" t="n">
-        <v>4435612.78</v>
+        <v>43486399.8</v>
       </c>
     </row>
     <row r="10">
@@ -26730,22 +26730,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>903528</v>
+        <v>1734966</v>
       </c>
       <c r="M10" t="n">
-        <v>232050</v>
+        <v>1187025</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>53550</v>
       </c>
       <c r="P10" t="n">
-        <v>900022.5</v>
+        <v>1180140</v>
       </c>
       <c r="Q10" t="n">
-        <v>2198187.72</v>
+        <v>21550860</v>
       </c>
     </row>
     <row r="11">
@@ -26783,22 +26783,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>318600</v>
+        <v>934200</v>
       </c>
       <c r="M11" t="n">
-        <v>160650</v>
+        <v>425250</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>8670</v>
       </c>
       <c r="P11" t="n">
-        <v>710775</v>
+        <v>866970</v>
       </c>
       <c r="Q11" t="n">
-        <v>716480.64</v>
+        <v>7024320</v>
       </c>
     </row>
     <row r="12">
@@ -26836,7 +26836,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>124200</v>
+        <v>534600</v>
       </c>
       <c r="M12" t="n">
         <v>9975</v>
@@ -26845,13 +26845,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P12" t="n">
-        <v>719550</v>
+        <v>614250</v>
       </c>
       <c r="Q12" t="n">
-        <v>257554.08</v>
+        <v>2525040</v>
       </c>
     </row>
     <row r="13">
@@ -26889,10 +26889,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>37800</v>
+        <v>583200</v>
       </c>
       <c r="M13" t="n">
-        <v>31500</v>
+        <v>10500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -26901,10 +26901,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1296750</v>
+        <v>1612650</v>
       </c>
       <c r="Q13" t="n">
-        <v>139793.04</v>
+        <v>1370520</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>27000</v>
+        <v>172800</v>
       </c>
       <c r="M14" t="n">
-        <v>189000</v>
+        <v>231000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P14" t="n">
-        <v>873600</v>
+        <v>900900</v>
       </c>
       <c r="Q14" t="n">
-        <v>93580.92</v>
+        <v>917460</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>10800</v>
+        <v>221400</v>
       </c>
       <c r="M15" t="n">
-        <v>52500</v>
+        <v>21000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P15" t="n">
-        <v>1216800</v>
+        <v>1682850</v>
       </c>
       <c r="Q15" t="n">
-        <v>67583.16</v>
+        <v>662580</v>
       </c>
     </row>
     <row r="16">
@@ -27048,22 +27048,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10800</v>
+        <v>232200</v>
       </c>
       <c r="M16" t="n">
-        <v>10500</v>
+        <v>42000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="P16" t="n">
-        <v>659100</v>
+        <v>1370850</v>
       </c>
       <c r="Q16" t="n">
-        <v>35141.04</v>
+        <v>344520</v>
       </c>
     </row>
     <row r="17">
@@ -27104,7 +27104,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -27113,10 +27113,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="Q17" t="n">
-        <v>4626.72</v>
+        <v>45360</v>
       </c>
     </row>
     <row r="18">
@@ -27157,7 +27157,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27169,7 +27169,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>440.64</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="19">
@@ -27210,7 +27210,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>63000</v>
+        <v>115500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -27222,7 +27222,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3855.6</v>
+        <v>37800</v>
       </c>
     </row>
     <row r="20">
@@ -27692,7 +27692,7 @@
         <v>110730</v>
       </c>
       <c r="H4" t="n">
-        <v>28470</v>
+        <v>29940</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -27704,7 +27704,7 @@
         <v>66</v>
       </c>
       <c r="L4" t="n">
-        <v>310110</v>
+        <v>361200</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>79770</v>
+        <v>84420</v>
       </c>
       <c r="P4" t="n">
-        <v>1200</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>29765.16</v>
+        <v>414451.62</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>54030</v>
       </c>
       <c r="H5" t="n">
-        <v>18690</v>
+        <v>20670</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>117150</v>
+        <v>131460</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>43020</v>
+        <v>49950</v>
       </c>
       <c r="P5" t="n">
-        <v>2790</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9877.85</v>
+        <v>137539.71</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>11010</v>
       </c>
       <c r="H6" t="n">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>25950</v>
+        <v>33300</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>14790</v>
+        <v>19170</v>
       </c>
       <c r="P6" t="n">
-        <v>3780</v>
+        <v>420</v>
       </c>
       <c r="Q6" t="n">
-        <v>1628.33</v>
+        <v>22672.98</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>630</v>
       </c>
       <c r="H7" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5130</v>
+        <v>6750</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4110</v>
+        <v>11280</v>
       </c>
       <c r="P7" t="n">
-        <v>4950</v>
+        <v>1140</v>
       </c>
       <c r="Q7" t="n">
-        <v>151.44</v>
+        <v>2108.7</v>
       </c>
     </row>
     <row r="8">
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>750</v>
+        <v>2520</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1320</v>
+        <v>5040</v>
       </c>
       <c r="P8" t="n">
-        <v>5760</v>
+        <v>4410</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.37</v>
+        <v>395.01</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>450</v>
+        <v>2370</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>150</v>
+        <v>1590</v>
       </c>
       <c r="P9" t="n">
-        <v>5130</v>
+        <v>10650</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.16</v>
+        <v>169.29</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
+        <v>1320</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28034,10 +28034,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2430</v>
+        <v>7200</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>35.64</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28087,10 +28087,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1020</v>
+        <v>3600</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="12">
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>120</v>
+        <v>660</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="13">
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6728.4</v>
+        <v>7441.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>5.96</v>
       </c>
       <c r="L5" t="n">
-        <v>24601.5</v>
+        <v>27606.6</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2151</v>
+        <v>2497.5</v>
       </c>
       <c r="P5" t="n">
-        <v>55.8</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>493.89</v>
+        <v>6876.99</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>550.5</v>
       </c>
       <c r="H6" t="n">
-        <v>684</v>
+        <v>889.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>9601.5</v>
+        <v>12321</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3697.5</v>
+        <v>4792.5</v>
       </c>
       <c r="P6" t="n">
-        <v>567</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
-        <v>1221.25</v>
+        <v>17004.74</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>94.5</v>
       </c>
       <c r="H7" t="n">
-        <v>306.6</v>
+        <v>350.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3078</v>
+        <v>4050</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1438.5</v>
+        <v>3948</v>
       </c>
       <c r="P7" t="n">
-        <v>1237.5</v>
+        <v>285</v>
       </c>
       <c r="Q7" t="n">
-        <v>121.15</v>
+        <v>1686.96</v>
       </c>
     </row>
     <row r="8">
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>532.5</v>
+        <v>1789.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>594</v>
+        <v>2268</v>
       </c>
       <c r="P8" t="n">
-        <v>2188.8</v>
+        <v>1675.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.95</v>
+        <v>375.26</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>364.5</v>
+        <v>1919.7</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>82.5</v>
+        <v>874.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2565</v>
+        <v>5325</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.79</v>
+        <v>164.21</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26.7</v>
+        <v>1174.8</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29326,10 +29326,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2065.5</v>
+        <v>6120</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>35.64</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29379,10 +29379,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>918</v>
+        <v>3240</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="12">
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>120</v>
+        <v>660</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="13">
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>38351880</v>
+        <v>42414840</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>289296.65</v>
       </c>
       <c r="L5" t="n">
-        <v>4428270</v>
+        <v>4969188</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>365670</v>
+        <v>424575</v>
       </c>
       <c r="P5" t="n">
-        <v>3627</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>296335.56</v>
+        <v>4126191.3</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>29727</v>
       </c>
       <c r="H6" t="n">
-        <v>3898800</v>
+        <v>5068440</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>1728270</v>
+        <v>2217780</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>628575</v>
+        <v>814725</v>
       </c>
       <c r="P6" t="n">
-        <v>36855</v>
+        <v>4095</v>
       </c>
       <c r="Q6" t="n">
-        <v>732749.49</v>
+        <v>10202841</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>5103</v>
       </c>
       <c r="H7" t="n">
-        <v>1747620</v>
+        <v>1997280</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>554040</v>
+        <v>729000</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>244545</v>
+        <v>671160</v>
       </c>
       <c r="P7" t="n">
-        <v>80437.5</v>
+        <v>18525</v>
       </c>
       <c r="Q7" t="n">
-        <v>72692.64</v>
+        <v>1012176</v>
       </c>
     </row>
     <row r="8">
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>95850</v>
+        <v>322056</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>100980</v>
+        <v>385560</v>
       </c>
       <c r="P8" t="n">
-        <v>142272</v>
+        <v>108927</v>
       </c>
       <c r="Q8" t="n">
-        <v>16170.27</v>
+        <v>225155.7</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>171000</v>
+        <v>1197000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>65610</v>
+        <v>345546</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14025</v>
+        <v>148665</v>
       </c>
       <c r="P9" t="n">
-        <v>166725</v>
+        <v>346125</v>
       </c>
       <c r="Q9" t="n">
-        <v>7076.01</v>
+        <v>98526.78</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171000</v>
+        <v>1026000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4806</v>
+        <v>211464</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30618,10 +30618,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>134257.5</v>
+        <v>397800</v>
       </c>
       <c r="Q10" t="n">
-        <v>1535.76</v>
+        <v>21384</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>129600</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30671,10 +30671,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>59670</v>
+        <v>210600</v>
       </c>
       <c r="Q11" t="n">
-        <v>213.3</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="12">
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7800</v>
+        <v>42900</v>
       </c>
       <c r="Q12" t="n">
-        <v>42.66</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13">
